--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Monthly/monthly_combined_bootstrap_summary_costs_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Monthly/monthly_combined_bootstrap_summary_costs_SOURCE.xlsx
@@ -506,34 +506,34 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>117.126</v>
+        <v>110.948</v>
       </c>
       <c r="D4">
-        <v>2.759</v>
+        <v>2.483</v>
       </c>
       <c r="E4">
-        <v>1.661</v>
+        <v>1.576</v>
       </c>
       <c r="F4">
-        <v>0.053</v>
+        <v>0.05</v>
       </c>
       <c r="G4">
-        <v>113.777</v>
+        <v>107.778</v>
       </c>
       <c r="H4">
-        <v>120.288</v>
+        <v>113.954</v>
       </c>
       <c r="I4">
-        <v>113.74</v>
+        <v>107.713</v>
       </c>
       <c r="J4">
-        <v>120.101</v>
+        <v>113.801</v>
       </c>
       <c r="K4">
-        <v>114.057</v>
+        <v>108.014</v>
       </c>
       <c r="L4">
-        <v>120.418</v>
+        <v>114.101</v>
       </c>
     </row>
     <row r="5">
@@ -546,34 +546,34 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>86.762</v>
+        <v>78.482</v>
       </c>
       <c r="D5">
-        <v>2.931</v>
+        <v>2.413</v>
       </c>
       <c r="E5">
-        <v>1.712</v>
+        <v>1.553</v>
       </c>
       <c r="F5">
-        <v>0.054</v>
+        <v>0.049</v>
       </c>
       <c r="G5">
-        <v>83.184</v>
+        <v>75.252</v>
       </c>
       <c r="H5">
-        <v>89.896</v>
+        <v>81.34099999999999</v>
       </c>
       <c r="I5">
-        <v>82.777</v>
+        <v>74.908</v>
       </c>
       <c r="J5">
-        <v>89.708</v>
+        <v>81.102</v>
       </c>
       <c r="K5">
-        <v>83.593</v>
+        <v>75.67700000000001</v>
       </c>
       <c r="L5">
-        <v>90.524</v>
+        <v>81.87</v>
       </c>
     </row>
     <row r="6">
@@ -586,34 +586,34 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>73.15300000000001</v>
+        <v>60.934</v>
       </c>
       <c r="D6">
-        <v>1.393</v>
+        <v>1.003</v>
       </c>
       <c r="E6">
-        <v>1.18</v>
+        <v>1.002</v>
       </c>
       <c r="F6">
-        <v>0.037</v>
+        <v>0.032</v>
       </c>
       <c r="G6">
-        <v>70.839</v>
+        <v>58.986</v>
       </c>
       <c r="H6">
-        <v>75.46599999999999</v>
+        <v>62.912</v>
       </c>
       <c r="I6">
-        <v>70.73099999999999</v>
+        <v>58.906</v>
       </c>
       <c r="J6">
-        <v>75.443</v>
+        <v>62.857</v>
       </c>
       <c r="K6">
-        <v>70.863</v>
+        <v>59.026</v>
       </c>
       <c r="L6">
-        <v>75.575</v>
+        <v>62.977</v>
       </c>
     </row>
     <row r="7">
@@ -626,34 +626,34 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>62.447</v>
+        <v>49.339</v>
       </c>
       <c r="D7">
-        <v>1.283</v>
+        <v>0.825</v>
       </c>
       <c r="E7">
-        <v>1.133</v>
+        <v>0.908</v>
       </c>
       <c r="F7">
-        <v>0.036</v>
+        <v>0.029</v>
       </c>
       <c r="G7">
-        <v>60.227</v>
+        <v>47.576</v>
       </c>
       <c r="H7">
-        <v>64.66800000000001</v>
+        <v>51.136</v>
       </c>
       <c r="I7">
-        <v>60.199</v>
+        <v>47.536</v>
       </c>
       <c r="J7">
-        <v>64.679</v>
+        <v>51.184</v>
       </c>
       <c r="K7">
-        <v>60.215</v>
+        <v>47.511</v>
       </c>
       <c r="L7">
-        <v>64.69499999999999</v>
+        <v>51.158</v>
       </c>
     </row>
     <row r="8">
@@ -666,34 +666,34 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>56.65</v>
+        <v>42.948</v>
       </c>
       <c r="D8">
-        <v>1.533</v>
+        <v>0.917</v>
       </c>
       <c r="E8">
-        <v>1.238</v>
+        <v>0.958</v>
       </c>
       <c r="F8">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="G8">
-        <v>54.221</v>
+        <v>41.081</v>
       </c>
       <c r="H8">
-        <v>59.074</v>
+        <v>44.836</v>
       </c>
       <c r="I8">
-        <v>54.112</v>
+        <v>40.93</v>
       </c>
       <c r="J8">
-        <v>58.982</v>
+        <v>44.717</v>
       </c>
       <c r="K8">
-        <v>54.315</v>
+        <v>41.19</v>
       </c>
       <c r="L8">
-        <v>59.185</v>
+        <v>44.977</v>
       </c>
     </row>
     <row r="9">
@@ -706,34 +706,34 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>51.219</v>
+        <v>37.392</v>
       </c>
       <c r="D9">
-        <v>1.371</v>
+        <v>0.755</v>
       </c>
       <c r="E9">
-        <v>1.171</v>
+        <v>0.869</v>
       </c>
       <c r="F9">
-        <v>0.037</v>
+        <v>0.027</v>
       </c>
       <c r="G9">
-        <v>48.922</v>
+        <v>35.704</v>
       </c>
       <c r="H9">
-        <v>53.512</v>
+        <v>39.11</v>
       </c>
       <c r="I9">
-        <v>48.917</v>
+        <v>35.735</v>
       </c>
       <c r="J9">
-        <v>53.526</v>
+        <v>39.163</v>
       </c>
       <c r="K9">
-        <v>48.91</v>
+        <v>35.636</v>
       </c>
       <c r="L9">
-        <v>53.519</v>
+        <v>39.064</v>
       </c>
     </row>
     <row r="10">
@@ -746,34 +746,34 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>47.448</v>
+        <v>33.456</v>
       </c>
       <c r="D10">
-        <v>1.211</v>
+        <v>0.618</v>
       </c>
       <c r="E10">
-        <v>1.101</v>
+        <v>0.786</v>
       </c>
       <c r="F10">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="G10">
-        <v>45.297</v>
+        <v>31.935</v>
       </c>
       <c r="H10">
-        <v>49.611</v>
+        <v>35.016</v>
       </c>
       <c r="I10">
-        <v>45.265</v>
+        <v>31.922</v>
       </c>
       <c r="J10">
-        <v>49.565</v>
+        <v>34.982</v>
       </c>
       <c r="K10">
-        <v>45.338</v>
+        <v>31.949</v>
       </c>
       <c r="L10">
-        <v>49.637</v>
+        <v>35.009</v>
       </c>
     </row>
     <row r="11">
@@ -786,34 +786,34 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>47.11</v>
+        <v>32.202</v>
       </c>
       <c r="D11">
-        <v>1.294</v>
+        <v>0.627</v>
       </c>
       <c r="E11">
-        <v>1.138</v>
+        <v>0.792</v>
       </c>
       <c r="F11">
-        <v>0.036</v>
+        <v>0.025</v>
       </c>
       <c r="G11">
-        <v>44.801</v>
+        <v>30.611</v>
       </c>
       <c r="H11">
-        <v>49.26</v>
+        <v>33.715</v>
       </c>
       <c r="I11">
-        <v>44.703</v>
+        <v>30.515</v>
       </c>
       <c r="J11">
-        <v>49.11</v>
+        <v>33.68</v>
       </c>
       <c r="K11">
-        <v>45.03</v>
+        <v>30.685</v>
       </c>
       <c r="L11">
-        <v>49.437</v>
+        <v>33.85</v>
       </c>
     </row>
     <row r="12">
@@ -826,34 +826,34 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>45.577</v>
+        <v>30.067</v>
       </c>
       <c r="D12">
-        <v>1.582</v>
+        <v>0.702</v>
       </c>
       <c r="E12">
-        <v>1.258</v>
+        <v>0.838</v>
       </c>
       <c r="F12">
-        <v>0.04</v>
+        <v>0.026</v>
       </c>
       <c r="G12">
-        <v>43.215</v>
+        <v>28.509</v>
       </c>
       <c r="H12">
-        <v>48.146</v>
+        <v>31.793</v>
       </c>
       <c r="I12">
-        <v>42.98</v>
+        <v>28.347</v>
       </c>
       <c r="J12">
-        <v>48.099</v>
+        <v>31.697</v>
       </c>
       <c r="K12">
-        <v>43.159</v>
+        <v>28.522</v>
       </c>
       <c r="L12">
-        <v>48.278</v>
+        <v>31.872</v>
       </c>
     </row>
     <row r="13">
@@ -866,34 +866,34 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>48.554</v>
+        <v>31.085</v>
       </c>
       <c r="D13">
-        <v>1.568</v>
+        <v>0.668</v>
       </c>
       <c r="E13">
-        <v>1.252</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="F13">
-        <v>0.04</v>
+        <v>0.026</v>
       </c>
       <c r="G13">
-        <v>46.019</v>
+        <v>29.449</v>
       </c>
       <c r="H13">
-        <v>50.927</v>
+        <v>32.653</v>
       </c>
       <c r="I13">
-        <v>45.955</v>
+        <v>29.398</v>
       </c>
       <c r="J13">
-        <v>50.883</v>
+        <v>32.657</v>
       </c>
       <c r="K13">
-        <v>46.144</v>
+        <v>29.479</v>
       </c>
       <c r="L13">
-        <v>51.072</v>
+        <v>32.738</v>
       </c>
     </row>
     <row r="14">
@@ -906,34 +906,34 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>42.449</v>
+        <v>26.265</v>
       </c>
       <c r="D14">
-        <v>1.212</v>
+        <v>0.482</v>
       </c>
       <c r="E14">
-        <v>1.101</v>
+        <v>0.694</v>
       </c>
       <c r="F14">
-        <v>0.035</v>
+        <v>0.022</v>
       </c>
       <c r="G14">
-        <v>40.254</v>
+        <v>24.894</v>
       </c>
       <c r="H14">
-        <v>44.57</v>
+        <v>27.614</v>
       </c>
       <c r="I14">
-        <v>40.157</v>
+        <v>24.815</v>
       </c>
       <c r="J14">
-        <v>44.459</v>
+        <v>27.514</v>
       </c>
       <c r="K14">
-        <v>40.402</v>
+        <v>25.006</v>
       </c>
       <c r="L14">
-        <v>44.704</v>
+        <v>27.704</v>
       </c>
     </row>
     <row r="15">
@@ -946,34 +946,34 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>44.795</v>
+        <v>26.879</v>
       </c>
       <c r="D15">
-        <v>1.357</v>
+        <v>0.513</v>
       </c>
       <c r="E15">
-        <v>1.165</v>
+        <v>0.716</v>
       </c>
       <c r="F15">
-        <v>0.037</v>
+        <v>0.023</v>
       </c>
       <c r="G15">
-        <v>42.506</v>
+        <v>25.489</v>
       </c>
       <c r="H15">
-        <v>47.073</v>
+        <v>28.296</v>
       </c>
       <c r="I15">
-        <v>42.345</v>
+        <v>25.386</v>
       </c>
       <c r="J15">
-        <v>47.052</v>
+        <v>28.22</v>
       </c>
       <c r="K15">
-        <v>42.533</v>
+        <v>25.552</v>
       </c>
       <c r="L15">
-        <v>47.24</v>
+        <v>28.385</v>
       </c>
     </row>
     <row r="16">
@@ -986,34 +986,34 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>43.043</v>
+        <v>25.065</v>
       </c>
       <c r="D16">
-        <v>1.489</v>
+        <v>0.521</v>
       </c>
       <c r="E16">
-        <v>1.22</v>
+        <v>0.722</v>
       </c>
       <c r="F16">
-        <v>0.039</v>
+        <v>0.023</v>
       </c>
       <c r="G16">
-        <v>40.602</v>
+        <v>23.636</v>
       </c>
       <c r="H16">
-        <v>45.385</v>
+        <v>26.465</v>
       </c>
       <c r="I16">
-        <v>40.461</v>
+        <v>23.58</v>
       </c>
       <c r="J16">
-        <v>45.384</v>
+        <v>26.493</v>
       </c>
       <c r="K16">
-        <v>40.652</v>
+        <v>23.622</v>
       </c>
       <c r="L16">
-        <v>45.575</v>
+        <v>26.535</v>
       </c>
     </row>
     <row r="17">
@@ -1026,34 +1026,34 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>43.662</v>
+        <v>24.628</v>
       </c>
       <c r="D17">
-        <v>1.492</v>
+        <v>0.49</v>
       </c>
       <c r="E17">
-        <v>1.222</v>
+        <v>0.7</v>
       </c>
       <c r="F17">
-        <v>0.039</v>
+        <v>0.022</v>
       </c>
       <c r="G17">
-        <v>41.27</v>
+        <v>23.268</v>
       </c>
       <c r="H17">
-        <v>46.059</v>
+        <v>26.013</v>
       </c>
       <c r="I17">
-        <v>41.348</v>
+        <v>23.297</v>
       </c>
       <c r="J17">
-        <v>45.853</v>
+        <v>25.926</v>
       </c>
       <c r="K17">
-        <v>41.474</v>
+        <v>23.343</v>
       </c>
       <c r="L17">
-        <v>45.979</v>
+        <v>25.972</v>
       </c>
     </row>
     <row r="18">
@@ -1066,34 +1066,34 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>45.173</v>
+        <v>24.642</v>
       </c>
       <c r="D18">
-        <v>1.528</v>
+        <v>0.473</v>
       </c>
       <c r="E18">
-        <v>1.236</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="F18">
-        <v>0.039</v>
+        <v>0.022</v>
       </c>
       <c r="G18">
-        <v>42.762</v>
+        <v>23.311</v>
       </c>
       <c r="H18">
-        <v>47.608</v>
+        <v>26.007</v>
       </c>
       <c r="I18">
-        <v>42.869</v>
+        <v>23.328</v>
       </c>
       <c r="J18">
-        <v>47.603</v>
+        <v>25.986</v>
       </c>
       <c r="K18">
-        <v>42.756</v>
+        <v>23.315</v>
       </c>
       <c r="L18">
-        <v>47.489</v>
+        <v>25.973</v>
       </c>
     </row>
     <row r="19">
@@ -1106,34 +1106,34 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>42.166</v>
+        <v>22.336</v>
       </c>
       <c r="D19">
-        <v>1.543</v>
+        <v>0.441</v>
       </c>
       <c r="E19">
-        <v>1.242</v>
+        <v>0.664</v>
       </c>
       <c r="F19">
-        <v>0.039</v>
+        <v>0.021</v>
       </c>
       <c r="G19">
-        <v>39.756</v>
+        <v>21.053</v>
       </c>
       <c r="H19">
-        <v>44.625</v>
+        <v>23.656</v>
       </c>
       <c r="I19">
-        <v>39.688</v>
+        <v>20.946</v>
       </c>
       <c r="J19">
-        <v>44.566</v>
+        <v>23.632</v>
       </c>
       <c r="K19">
-        <v>39.79</v>
+        <v>21.058</v>
       </c>
       <c r="L19">
-        <v>44.668</v>
+        <v>23.744</v>
       </c>
     </row>
     <row r="20">
@@ -1146,34 +1146,34 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>43.277</v>
+        <v>22.268</v>
       </c>
       <c r="D20">
-        <v>4.928</v>
+        <v>1.307</v>
       </c>
       <c r="E20">
-        <v>2.22</v>
+        <v>1.143</v>
       </c>
       <c r="F20">
-        <v>0.07000000000000001</v>
+        <v>0.036</v>
       </c>
       <c r="G20">
-        <v>38.955</v>
+        <v>20.046</v>
       </c>
       <c r="H20">
-        <v>47.656</v>
+        <v>24.527</v>
       </c>
       <c r="I20">
-        <v>38.24</v>
+        <v>19.653</v>
       </c>
       <c r="J20">
-        <v>46.701</v>
+        <v>24.134</v>
       </c>
       <c r="K20">
-        <v>39.882</v>
+        <v>20.42</v>
       </c>
       <c r="L20">
-        <v>48.342</v>
+        <v>24.901</v>
       </c>
     </row>
     <row r="21">
@@ -1186,34 +1186,34 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>42.227</v>
+        <v>21.095</v>
       </c>
       <c r="D21">
-        <v>1.549</v>
+        <v>0.41</v>
       </c>
       <c r="E21">
-        <v>1.245</v>
+        <v>0.64</v>
       </c>
       <c r="F21">
-        <v>0.039</v>
+        <v>0.02</v>
       </c>
       <c r="G21">
-        <v>39.764</v>
+        <v>19.832</v>
       </c>
       <c r="H21">
-        <v>44.643</v>
+        <v>22.342</v>
       </c>
       <c r="I21">
-        <v>39.798</v>
+        <v>19.837</v>
       </c>
       <c r="J21">
-        <v>44.589</v>
+        <v>22.327</v>
       </c>
       <c r="K21">
-        <v>39.841</v>
+        <v>19.855</v>
       </c>
       <c r="L21">
-        <v>44.632</v>
+        <v>22.345</v>
       </c>
     </row>
     <row r="22">
@@ -1226,34 +1226,34 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>42.192</v>
+        <v>20.388</v>
       </c>
       <c r="D22">
-        <v>1.724</v>
+        <v>0.421</v>
       </c>
       <c r="E22">
-        <v>1.313</v>
+        <v>0.649</v>
       </c>
       <c r="F22">
-        <v>0.042</v>
+        <v>0.021</v>
       </c>
       <c r="G22">
-        <v>39.577</v>
+        <v>19.1</v>
       </c>
       <c r="H22">
-        <v>44.724</v>
+        <v>21.642</v>
       </c>
       <c r="I22">
-        <v>39.526</v>
+        <v>19.073</v>
       </c>
       <c r="J22">
-        <v>44.735</v>
+        <v>21.624</v>
       </c>
       <c r="K22">
-        <v>39.608</v>
+        <v>19.134</v>
       </c>
       <c r="L22">
-        <v>44.816</v>
+        <v>21.686</v>
       </c>
     </row>
     <row r="23">
@@ -1266,34 +1266,34 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>39.602</v>
+        <v>18.511</v>
       </c>
       <c r="D23">
-        <v>1.402</v>
+        <v>0.33</v>
       </c>
       <c r="E23">
-        <v>1.184</v>
+        <v>0.574</v>
       </c>
       <c r="F23">
-        <v>0.037</v>
+        <v>0.018</v>
       </c>
       <c r="G23">
-        <v>37.211</v>
+        <v>17.358</v>
       </c>
       <c r="H23">
-        <v>41.851</v>
+        <v>19.61</v>
       </c>
       <c r="I23">
-        <v>37.224</v>
+        <v>17.35</v>
       </c>
       <c r="J23">
-        <v>41.853</v>
+        <v>19.626</v>
       </c>
       <c r="K23">
-        <v>37.28</v>
+        <v>17.369</v>
       </c>
       <c r="L23">
-        <v>41.908</v>
+        <v>19.644</v>
       </c>
     </row>
     <row r="24">
@@ -1306,34 +1306,34 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>40.29</v>
+        <v>18.213</v>
       </c>
       <c r="D24">
-        <v>1.801</v>
+        <v>0.393</v>
       </c>
       <c r="E24">
-        <v>1.342</v>
+        <v>0.627</v>
       </c>
       <c r="F24">
-        <v>0.042</v>
+        <v>0.02</v>
       </c>
       <c r="G24">
-        <v>37.647</v>
+        <v>16.989</v>
       </c>
       <c r="H24">
-        <v>42.908</v>
+        <v>19.447</v>
       </c>
       <c r="I24">
-        <v>37.569</v>
+        <v>17.001</v>
       </c>
       <c r="J24">
-        <v>42.816</v>
+        <v>19.41</v>
       </c>
       <c r="K24">
-        <v>37.751</v>
+        <v>17.021</v>
       </c>
       <c r="L24">
-        <v>42.998</v>
+        <v>19.429</v>
       </c>
     </row>
     <row r="25">
@@ -1346,34 +1346,34 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>37.777</v>
+        <v>16.526</v>
       </c>
       <c r="D25">
-        <v>1.39</v>
+        <v>0.283</v>
       </c>
       <c r="E25">
-        <v>1.179</v>
+        <v>0.532</v>
       </c>
       <c r="F25">
-        <v>0.037</v>
+        <v>0.017</v>
       </c>
       <c r="G25">
-        <v>35.421</v>
+        <v>15.473</v>
       </c>
       <c r="H25">
-        <v>40.042</v>
+        <v>17.558</v>
       </c>
       <c r="I25">
-        <v>35.403</v>
+        <v>15.438</v>
       </c>
       <c r="J25">
-        <v>40.037</v>
+        <v>17.533</v>
       </c>
       <c r="K25">
-        <v>35.471</v>
+        <v>15.509</v>
       </c>
       <c r="L25">
-        <v>40.105</v>
+        <v>17.604</v>
       </c>
     </row>
     <row r="26">
@@ -1466,34 +1466,34 @@
         <v>3</v>
       </c>
       <c r="C28">
-        <v>129.054</v>
+        <v>123.894</v>
       </c>
       <c r="D28">
-        <v>3.171</v>
+        <v>2.941</v>
       </c>
       <c r="E28">
-        <v>1.781</v>
+        <v>1.715</v>
       </c>
       <c r="F28">
-        <v>0.056</v>
+        <v>0.054</v>
       </c>
       <c r="G28">
-        <v>125.486</v>
+        <v>120.448</v>
       </c>
       <c r="H28">
-        <v>132.466</v>
+        <v>127.171</v>
       </c>
       <c r="I28">
-        <v>125.442</v>
+        <v>120.446</v>
       </c>
       <c r="J28">
-        <v>132.433</v>
+        <v>127.184</v>
       </c>
       <c r="K28">
-        <v>125.596</v>
+        <v>120.521</v>
       </c>
       <c r="L28">
-        <v>132.588</v>
+        <v>127.259</v>
       </c>
     </row>
     <row r="29">
@@ -1506,34 +1506,34 @@
         <v>4</v>
       </c>
       <c r="C29">
-        <v>94.794</v>
+        <v>87.569</v>
       </c>
       <c r="D29">
-        <v>3.234</v>
+        <v>2.779</v>
       </c>
       <c r="E29">
-        <v>1.798</v>
+        <v>1.667</v>
       </c>
       <c r="F29">
-        <v>0.057</v>
+        <v>0.053</v>
       </c>
       <c r="G29">
-        <v>91.21299999999999</v>
+        <v>84.241</v>
       </c>
       <c r="H29">
-        <v>98.26300000000001</v>
+        <v>90.77500000000001</v>
       </c>
       <c r="I29">
-        <v>90.955</v>
+        <v>83.99299999999999</v>
       </c>
       <c r="J29">
-        <v>98.036</v>
+        <v>90.521</v>
       </c>
       <c r="K29">
-        <v>91.496</v>
+        <v>84.556</v>
       </c>
       <c r="L29">
-        <v>98.577</v>
+        <v>91.084</v>
       </c>
     </row>
     <row r="30">
@@ -1546,34 +1546,34 @@
         <v>5</v>
       </c>
       <c r="C30">
-        <v>79.58</v>
+        <v>68.077</v>
       </c>
       <c r="D30">
-        <v>1.744</v>
+        <v>1.319</v>
       </c>
       <c r="E30">
-        <v>1.32</v>
+        <v>1.149</v>
       </c>
       <c r="F30">
-        <v>0.042</v>
+        <v>0.036</v>
       </c>
       <c r="G30">
-        <v>76.95099999999999</v>
+        <v>65.782</v>
       </c>
       <c r="H30">
-        <v>82.127</v>
+        <v>70.28400000000001</v>
       </c>
       <c r="I30">
-        <v>76.825</v>
+        <v>65.759</v>
       </c>
       <c r="J30">
-        <v>82.038</v>
+        <v>70.239</v>
       </c>
       <c r="K30">
-        <v>77.08</v>
+        <v>65.871</v>
       </c>
       <c r="L30">
-        <v>82.294</v>
+        <v>70.351</v>
       </c>
     </row>
     <row r="31">
@@ -1586,34 +1586,34 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>67.54000000000001</v>
+        <v>55.067</v>
       </c>
       <c r="D31">
-        <v>1.516</v>
+        <v>1.042</v>
       </c>
       <c r="E31">
-        <v>1.231</v>
+        <v>1.021</v>
       </c>
       <c r="F31">
-        <v>0.039</v>
+        <v>0.032</v>
       </c>
       <c r="G31">
-        <v>65.232</v>
+        <v>53.146</v>
       </c>
       <c r="H31">
-        <v>70.05800000000001</v>
+        <v>57.148</v>
       </c>
       <c r="I31">
-        <v>65.33199999999999</v>
+        <v>53.2</v>
       </c>
       <c r="J31">
-        <v>70.068</v>
+        <v>57.188</v>
       </c>
       <c r="K31">
-        <v>65.11799999999999</v>
+        <v>53.027</v>
       </c>
       <c r="L31">
-        <v>69.85299999999999</v>
+        <v>57.014</v>
       </c>
     </row>
     <row r="32">
@@ -1626,34 +1626,34 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <v>61.112</v>
+        <v>47.926</v>
       </c>
       <c r="D32">
-        <v>1.586</v>
+        <v>1.003</v>
       </c>
       <c r="E32">
-        <v>1.259</v>
+        <v>1.002</v>
       </c>
       <c r="F32">
-        <v>0.04</v>
+        <v>0.032</v>
       </c>
       <c r="G32">
-        <v>58.76</v>
+        <v>46.045</v>
       </c>
       <c r="H32">
-        <v>63.696</v>
+        <v>49.971</v>
       </c>
       <c r="I32">
-        <v>58.806</v>
+        <v>46.023</v>
       </c>
       <c r="J32">
-        <v>63.59</v>
+        <v>49.927</v>
       </c>
       <c r="K32">
-        <v>58.75</v>
+        <v>46.007</v>
       </c>
       <c r="L32">
-        <v>63.533</v>
+        <v>49.911</v>
       </c>
     </row>
     <row r="33">
@@ -1666,34 +1666,34 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <v>55.146</v>
+        <v>41.748</v>
       </c>
       <c r="D33">
-        <v>1.577</v>
+        <v>0.926</v>
       </c>
       <c r="E33">
-        <v>1.256</v>
+        <v>0.962</v>
       </c>
       <c r="F33">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="G33">
-        <v>52.736</v>
+        <v>39.896</v>
       </c>
       <c r="H33">
-        <v>57.659</v>
+        <v>43.667</v>
       </c>
       <c r="I33">
-        <v>52.643</v>
+        <v>39.851</v>
       </c>
       <c r="J33">
-        <v>57.509</v>
+        <v>43.517</v>
       </c>
       <c r="K33">
-        <v>52.834</v>
+        <v>40.012</v>
       </c>
       <c r="L33">
-        <v>57.701</v>
+        <v>43.678</v>
       </c>
     </row>
     <row r="34">
@@ -1706,34 +1706,34 @@
         <v>9</v>
       </c>
       <c r="C34">
-        <v>51.055</v>
+        <v>37.389</v>
       </c>
       <c r="D34">
-        <v>1.417</v>
+        <v>0.789</v>
       </c>
       <c r="E34">
-        <v>1.19</v>
+        <v>0.888</v>
       </c>
       <c r="F34">
-        <v>0.038</v>
+        <v>0.028</v>
       </c>
       <c r="G34">
-        <v>48.686</v>
+        <v>35.614</v>
       </c>
       <c r="H34">
-        <v>53.352</v>
+        <v>39.096</v>
       </c>
       <c r="I34">
-        <v>48.697</v>
+        <v>35.694</v>
       </c>
       <c r="J34">
-        <v>53.462</v>
+        <v>39.103</v>
       </c>
       <c r="K34">
-        <v>48.612</v>
+        <v>35.64</v>
       </c>
       <c r="L34">
-        <v>53.377</v>
+        <v>39.05</v>
       </c>
     </row>
     <row r="35">
@@ -1746,34 +1746,34 @@
         <v>10</v>
       </c>
       <c r="C35">
-        <v>50.524</v>
+        <v>35.92</v>
       </c>
       <c r="D35">
-        <v>1.385</v>
+        <v>0.732</v>
       </c>
       <c r="E35">
-        <v>1.177</v>
+        <v>0.856</v>
       </c>
       <c r="F35">
-        <v>0.037</v>
+        <v>0.027</v>
       </c>
       <c r="G35">
-        <v>48.279</v>
+        <v>34.281</v>
       </c>
       <c r="H35">
-        <v>52.892</v>
+        <v>37.635</v>
       </c>
       <c r="I35">
-        <v>48.211</v>
+        <v>34.185</v>
       </c>
       <c r="J35">
-        <v>52.883</v>
+        <v>37.591</v>
       </c>
       <c r="K35">
-        <v>48.226</v>
+        <v>34.287</v>
       </c>
       <c r="L35">
-        <v>52.898</v>
+        <v>37.693</v>
       </c>
     </row>
     <row r="36">
@@ -1786,34 +1786,34 @@
         <v>11</v>
       </c>
       <c r="C36">
-        <v>48.893</v>
+        <v>33.59</v>
       </c>
       <c r="D36">
-        <v>1.633</v>
+        <v>0.799</v>
       </c>
       <c r="E36">
-        <v>1.278</v>
+        <v>0.894</v>
       </c>
       <c r="F36">
-        <v>0.04</v>
+        <v>0.028</v>
       </c>
       <c r="G36">
-        <v>46.492</v>
+        <v>31.905</v>
       </c>
       <c r="H36">
-        <v>51.501</v>
+        <v>35.409</v>
       </c>
       <c r="I36">
-        <v>46.293</v>
+        <v>31.788</v>
       </c>
       <c r="J36">
-        <v>51.505</v>
+        <v>35.433</v>
       </c>
       <c r="K36">
-        <v>46.385</v>
+        <v>31.814</v>
       </c>
       <c r="L36">
-        <v>51.597</v>
+        <v>35.459</v>
       </c>
     </row>
     <row r="37">
@@ -1826,34 +1826,34 @@
         <v>12</v>
       </c>
       <c r="C37">
-        <v>52.007</v>
+        <v>34.704</v>
       </c>
       <c r="D37">
-        <v>1.633</v>
+        <v>0.76</v>
       </c>
       <c r="E37">
-        <v>1.278</v>
+        <v>0.872</v>
       </c>
       <c r="F37">
-        <v>0.04</v>
+        <v>0.028</v>
       </c>
       <c r="G37">
-        <v>49.48</v>
+        <v>32.976</v>
       </c>
       <c r="H37">
-        <v>54.489</v>
+        <v>36.393</v>
       </c>
       <c r="I37">
-        <v>49.253</v>
+        <v>32.837</v>
       </c>
       <c r="J37">
-        <v>54.368</v>
+        <v>36.313</v>
       </c>
       <c r="K37">
-        <v>49.624</v>
+        <v>33.075</v>
       </c>
       <c r="L37">
-        <v>54.739</v>
+        <v>36.551</v>
       </c>
     </row>
     <row r="38">
@@ -1866,34 +1866,34 @@
         <v>13</v>
       </c>
       <c r="C38">
-        <v>45.338</v>
+        <v>29.274</v>
       </c>
       <c r="D38">
-        <v>1.327</v>
+        <v>0.58</v>
       </c>
       <c r="E38">
-        <v>1.152</v>
+        <v>0.762</v>
       </c>
       <c r="F38">
-        <v>0.036</v>
+        <v>0.024</v>
       </c>
       <c r="G38">
-        <v>43.236</v>
+        <v>27.883</v>
       </c>
       <c r="H38">
-        <v>47.75</v>
+        <v>30.868</v>
       </c>
       <c r="I38">
-        <v>43.193</v>
+        <v>27.834</v>
       </c>
       <c r="J38">
-        <v>47.732</v>
+        <v>30.901</v>
       </c>
       <c r="K38">
-        <v>43.1</v>
+        <v>27.748</v>
       </c>
       <c r="L38">
-        <v>47.639</v>
+        <v>30.815</v>
       </c>
     </row>
     <row r="39">
@@ -1906,34 +1906,34 @@
         <v>14</v>
       </c>
       <c r="C39">
-        <v>47.779</v>
+        <v>29.973</v>
       </c>
       <c r="D39">
-        <v>1.606</v>
+        <v>0.671</v>
       </c>
       <c r="E39">
-        <v>1.267</v>
+        <v>0.819</v>
       </c>
       <c r="F39">
-        <v>0.04</v>
+        <v>0.026</v>
       </c>
       <c r="G39">
-        <v>45.457</v>
+        <v>28.469</v>
       </c>
       <c r="H39">
-        <v>50.424</v>
+        <v>31.68</v>
       </c>
       <c r="I39">
-        <v>45.297</v>
+        <v>28.306</v>
       </c>
       <c r="J39">
-        <v>50.437</v>
+        <v>31.65</v>
       </c>
       <c r="K39">
-        <v>45.283</v>
+        <v>28.397</v>
       </c>
       <c r="L39">
-        <v>50.423</v>
+        <v>31.741</v>
       </c>
     </row>
     <row r="40">
@@ -1946,34 +1946,34 @@
         <v>15</v>
       </c>
       <c r="C40">
-        <v>45.952</v>
+        <v>27.976</v>
       </c>
       <c r="D40">
-        <v>1.499</v>
+        <v>0.583</v>
       </c>
       <c r="E40">
-        <v>1.224</v>
+        <v>0.764</v>
       </c>
       <c r="F40">
-        <v>0.039</v>
+        <v>0.024</v>
       </c>
       <c r="G40">
-        <v>43.579</v>
+        <v>26.491</v>
       </c>
       <c r="H40">
-        <v>48.378</v>
+        <v>29.485</v>
       </c>
       <c r="I40">
-        <v>43.503</v>
+        <v>26.407</v>
       </c>
       <c r="J40">
-        <v>48.39</v>
+        <v>29.457</v>
       </c>
       <c r="K40">
-        <v>43.54</v>
+        <v>26.507</v>
       </c>
       <c r="L40">
-        <v>48.427</v>
+        <v>29.557</v>
       </c>
     </row>
     <row r="41">
@@ -1986,34 +1986,34 @@
         <v>16</v>
       </c>
       <c r="C41">
-        <v>46.636</v>
+        <v>27.536</v>
       </c>
       <c r="D41">
-        <v>1.593</v>
+        <v>0.596</v>
       </c>
       <c r="E41">
-        <v>1.262</v>
+        <v>0.772</v>
       </c>
       <c r="F41">
-        <v>0.04</v>
+        <v>0.024</v>
       </c>
       <c r="G41">
-        <v>44.08</v>
+        <v>25.97</v>
       </c>
       <c r="H41">
-        <v>49.026</v>
+        <v>28.995</v>
       </c>
       <c r="I41">
-        <v>44.006</v>
+        <v>25.932</v>
       </c>
       <c r="J41">
-        <v>49.003</v>
+        <v>28.935</v>
       </c>
       <c r="K41">
-        <v>44.186</v>
+        <v>26.084</v>
       </c>
       <c r="L41">
-        <v>49.183</v>
+        <v>29.087</v>
       </c>
     </row>
     <row r="42">
@@ -2026,34 +2026,34 @@
         <v>17</v>
       </c>
       <c r="C42">
-        <v>48.144</v>
+        <v>27.504</v>
       </c>
       <c r="D42">
-        <v>1.721</v>
+        <v>0.592</v>
       </c>
       <c r="E42">
-        <v>1.312</v>
+        <v>0.769</v>
       </c>
       <c r="F42">
-        <v>0.041</v>
+        <v>0.024</v>
       </c>
       <c r="G42">
-        <v>45.667</v>
+        <v>26.043</v>
       </c>
       <c r="H42">
-        <v>50.809</v>
+        <v>29.059</v>
       </c>
       <c r="I42">
-        <v>45.798</v>
+        <v>26.072</v>
       </c>
       <c r="J42">
-        <v>50.8</v>
+        <v>29.013</v>
       </c>
       <c r="K42">
-        <v>45.583</v>
+        <v>26.042</v>
       </c>
       <c r="L42">
-        <v>50.584</v>
+        <v>28.983</v>
       </c>
     </row>
     <row r="43">
@@ -2066,34 +2066,34 @@
         <v>18</v>
       </c>
       <c r="C43">
-        <v>44.998</v>
+        <v>24.959</v>
       </c>
       <c r="D43">
-        <v>1.638</v>
+        <v>0.526</v>
       </c>
       <c r="E43">
-        <v>1.28</v>
+        <v>0.725</v>
       </c>
       <c r="F43">
-        <v>0.04</v>
+        <v>0.023</v>
       </c>
       <c r="G43">
-        <v>42.481</v>
+        <v>23.527</v>
       </c>
       <c r="H43">
-        <v>47.499</v>
+        <v>26.368</v>
       </c>
       <c r="I43">
-        <v>42.465</v>
+        <v>23.491</v>
       </c>
       <c r="J43">
-        <v>47.421</v>
+        <v>26.347</v>
       </c>
       <c r="K43">
-        <v>42.567</v>
+        <v>23.559</v>
       </c>
       <c r="L43">
-        <v>47.522</v>
+        <v>26.416</v>
       </c>
     </row>
     <row r="44">
@@ -2106,34 +2106,34 @@
         <v>19</v>
       </c>
       <c r="C44">
-        <v>46.045</v>
+        <v>24.834</v>
       </c>
       <c r="D44">
-        <v>4.863</v>
+        <v>1.448</v>
       </c>
       <c r="E44">
-        <v>2.205</v>
+        <v>1.203</v>
       </c>
       <c r="F44">
-        <v>0.07000000000000001</v>
+        <v>0.038</v>
       </c>
       <c r="G44">
-        <v>41.895</v>
+        <v>22.562</v>
       </c>
       <c r="H44">
-        <v>50.539</v>
+        <v>27.279</v>
       </c>
       <c r="I44">
-        <v>41.57</v>
+        <v>22.28</v>
       </c>
       <c r="J44">
-        <v>49.834</v>
+        <v>26.944</v>
       </c>
       <c r="K44">
-        <v>42.429</v>
+        <v>22.811</v>
       </c>
       <c r="L44">
-        <v>50.693</v>
+        <v>27.474</v>
       </c>
     </row>
     <row r="45">
@@ -2146,34 +2146,34 @@
         <v>20</v>
       </c>
       <c r="C45">
-        <v>45.003</v>
+        <v>23.567</v>
       </c>
       <c r="D45">
-        <v>1.783</v>
+        <v>0.524</v>
       </c>
       <c r="E45">
-        <v>1.335</v>
+        <v>0.724</v>
       </c>
       <c r="F45">
-        <v>0.042</v>
+        <v>0.023</v>
       </c>
       <c r="G45">
-        <v>42.343</v>
+        <v>22.119</v>
       </c>
       <c r="H45">
-        <v>47.577</v>
+        <v>24.957</v>
       </c>
       <c r="I45">
-        <v>42.309</v>
+        <v>22.115</v>
       </c>
       <c r="J45">
-        <v>47.41</v>
+        <v>24.881</v>
       </c>
       <c r="K45">
-        <v>42.553</v>
+        <v>22.224</v>
       </c>
       <c r="L45">
-        <v>47.654</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="46">
@@ -2186,34 +2186,34 @@
         <v>21</v>
       </c>
       <c r="C46">
-        <v>44.959</v>
+        <v>22.774</v>
       </c>
       <c r="D46">
-        <v>1.883</v>
+        <v>0.518</v>
       </c>
       <c r="E46">
-        <v>1.372</v>
+        <v>0.72</v>
       </c>
       <c r="F46">
-        <v>0.043</v>
+        <v>0.023</v>
       </c>
       <c r="G46">
-        <v>42.224</v>
+        <v>21.331</v>
       </c>
       <c r="H46">
-        <v>47.603</v>
+        <v>24.153</v>
       </c>
       <c r="I46">
-        <v>42.094</v>
+        <v>21.282</v>
       </c>
       <c r="J46">
-        <v>47.526</v>
+        <v>24.085</v>
       </c>
       <c r="K46">
-        <v>42.346</v>
+        <v>21.431</v>
       </c>
       <c r="L46">
-        <v>47.778</v>
+        <v>24.234</v>
       </c>
     </row>
     <row r="47">
@@ -2226,34 +2226,34 @@
         <v>22</v>
       </c>
       <c r="C47">
-        <v>42.057</v>
+        <v>20.626</v>
       </c>
       <c r="D47">
-        <v>1.672</v>
+        <v>0.428</v>
       </c>
       <c r="E47">
-        <v>1.293</v>
+        <v>0.654</v>
       </c>
       <c r="F47">
-        <v>0.041</v>
+        <v>0.021</v>
       </c>
       <c r="G47">
-        <v>39.666</v>
+        <v>19.404</v>
       </c>
       <c r="H47">
-        <v>44.735</v>
+        <v>21.968</v>
       </c>
       <c r="I47">
-        <v>39.81</v>
+        <v>19.473</v>
       </c>
       <c r="J47">
-        <v>44.684</v>
+        <v>21.935</v>
       </c>
       <c r="K47">
-        <v>39.574</v>
+        <v>19.377</v>
       </c>
       <c r="L47">
-        <v>44.447</v>
+        <v>21.84</v>
       </c>
     </row>
     <row r="48">
@@ -2266,34 +2266,34 @@
         <v>23</v>
       </c>
       <c r="C48">
-        <v>42.887</v>
+        <v>20.365</v>
       </c>
       <c r="D48">
-        <v>2.037</v>
+        <v>0.49</v>
       </c>
       <c r="E48">
-        <v>1.427</v>
+        <v>0.7</v>
       </c>
       <c r="F48">
-        <v>0.045</v>
+        <v>0.022</v>
       </c>
       <c r="G48">
-        <v>40.019</v>
+        <v>18.945</v>
       </c>
       <c r="H48">
-        <v>45.613</v>
+        <v>21.69</v>
       </c>
       <c r="I48">
-        <v>40.018</v>
+        <v>18.941</v>
       </c>
       <c r="J48">
-        <v>45.535</v>
+        <v>21.656</v>
       </c>
       <c r="K48">
-        <v>40.168</v>
+        <v>19.027</v>
       </c>
       <c r="L48">
-        <v>45.685</v>
+        <v>21.742</v>
       </c>
     </row>
     <row r="49">
@@ -2306,34 +2306,34 @@
         <v>24</v>
       </c>
       <c r="C49">
-        <v>40.172</v>
+        <v>18.464</v>
       </c>
       <c r="D49">
-        <v>1.546</v>
+        <v>0.347</v>
       </c>
       <c r="E49">
-        <v>1.243</v>
+        <v>0.589</v>
       </c>
       <c r="F49">
-        <v>0.039</v>
+        <v>0.019</v>
       </c>
       <c r="G49">
-        <v>37.706</v>
+        <v>17.281</v>
       </c>
       <c r="H49">
-        <v>42.579</v>
+        <v>19.589</v>
       </c>
       <c r="I49">
-        <v>37.572</v>
+        <v>17.16</v>
       </c>
       <c r="J49">
-        <v>42.443</v>
+        <v>19.585</v>
       </c>
       <c r="K49">
-        <v>37.871</v>
+        <v>17.314</v>
       </c>
       <c r="L49">
-        <v>42.742</v>
+        <v>19.739</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Monthly/monthly_combined_bootstrap_summary_costs_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Monthly/monthly_combined_bootstrap_summary_costs_SOURCE.xlsx
@@ -426,34 +426,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>260.026</v>
+        <v>264.802</v>
       </c>
       <c r="D2">
-        <v>6.343</v>
+        <v>6.013</v>
       </c>
       <c r="E2">
-        <v>2.519</v>
+        <v>2.452</v>
       </c>
       <c r="F2">
-        <v>0.08</v>
+        <v>0.078</v>
       </c>
       <c r="G2">
-        <v>255.164</v>
+        <v>260.068</v>
       </c>
       <c r="H2">
-        <v>265.037</v>
+        <v>269.68</v>
       </c>
       <c r="I2">
-        <v>255.503</v>
+        <v>260.436</v>
       </c>
       <c r="J2">
-        <v>265.092</v>
+        <v>269.786</v>
       </c>
       <c r="K2">
-        <v>255.034</v>
+        <v>259.889</v>
       </c>
       <c r="L2">
-        <v>264.624</v>
+        <v>269.24</v>
       </c>
     </row>
     <row r="3">
@@ -466,34 +466,34 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>167.696</v>
+        <v>171.221</v>
       </c>
       <c r="D3">
-        <v>3.572</v>
+        <v>3.485</v>
       </c>
       <c r="E3">
-        <v>1.89</v>
+        <v>1.867</v>
       </c>
       <c r="F3">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="G3">
-        <v>163.993</v>
+        <v>167.564</v>
       </c>
       <c r="H3">
-        <v>171.401</v>
+        <v>174.882</v>
       </c>
       <c r="I3">
-        <v>163.97</v>
+        <v>167.525</v>
       </c>
       <c r="J3">
-        <v>171.371</v>
+        <v>174.859</v>
       </c>
       <c r="K3">
-        <v>164.022</v>
+        <v>167.585</v>
       </c>
       <c r="L3">
-        <v>171.423</v>
+        <v>174.919</v>
       </c>
     </row>
     <row r="4">
@@ -506,34 +506,34 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>110.948</v>
+        <v>114.154</v>
       </c>
       <c r="D4">
-        <v>2.483</v>
+        <v>2.293</v>
       </c>
       <c r="E4">
-        <v>1.576</v>
+        <v>1.514</v>
       </c>
       <c r="F4">
-        <v>0.05</v>
+        <v>0.048</v>
       </c>
       <c r="G4">
-        <v>107.778</v>
+        <v>111.106</v>
       </c>
       <c r="H4">
-        <v>113.954</v>
+        <v>117.042</v>
       </c>
       <c r="I4">
-        <v>107.713</v>
+        <v>111.077</v>
       </c>
       <c r="J4">
-        <v>113.801</v>
+        <v>116.973</v>
       </c>
       <c r="K4">
-        <v>108.014</v>
+        <v>111.255</v>
       </c>
       <c r="L4">
-        <v>114.101</v>
+        <v>117.151</v>
       </c>
     </row>
     <row r="5">
@@ -546,34 +546,34 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>78.482</v>
+        <v>81.008</v>
       </c>
       <c r="D5">
-        <v>2.413</v>
+        <v>2.391</v>
       </c>
       <c r="E5">
-        <v>1.553</v>
+        <v>1.546</v>
       </c>
       <c r="F5">
         <v>0.049</v>
       </c>
       <c r="G5">
-        <v>75.252</v>
+        <v>77.797</v>
       </c>
       <c r="H5">
-        <v>81.34099999999999</v>
+        <v>83.858</v>
       </c>
       <c r="I5">
-        <v>74.908</v>
+        <v>77.35599999999999</v>
       </c>
       <c r="J5">
-        <v>81.102</v>
+        <v>83.64100000000001</v>
       </c>
       <c r="K5">
-        <v>75.67700000000001</v>
+        <v>78.194</v>
       </c>
       <c r="L5">
-        <v>81.87</v>
+        <v>84.48</v>
       </c>
     </row>
     <row r="6">
@@ -586,34 +586,34 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>60.934</v>
+        <v>62.851</v>
       </c>
       <c r="D6">
-        <v>1.003</v>
+        <v>1.043</v>
       </c>
       <c r="E6">
-        <v>1.002</v>
+        <v>1.021</v>
       </c>
       <c r="F6">
         <v>0.032</v>
       </c>
       <c r="G6">
-        <v>58.986</v>
+        <v>60.867</v>
       </c>
       <c r="H6">
-        <v>62.912</v>
+        <v>64.871</v>
       </c>
       <c r="I6">
-        <v>58.906</v>
+        <v>60.801</v>
       </c>
       <c r="J6">
-        <v>62.857</v>
+        <v>64.843</v>
       </c>
       <c r="K6">
-        <v>59.026</v>
+        <v>60.877</v>
       </c>
       <c r="L6">
-        <v>62.977</v>
+        <v>64.91800000000001</v>
       </c>
     </row>
     <row r="7">
@@ -626,34 +626,34 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>49.339</v>
+        <v>50.917</v>
       </c>
       <c r="D7">
-        <v>0.825</v>
+        <v>0.857</v>
       </c>
       <c r="E7">
-        <v>0.908</v>
+        <v>0.926</v>
       </c>
       <c r="F7">
         <v>0.029</v>
       </c>
       <c r="G7">
-        <v>47.576</v>
+        <v>49.13</v>
       </c>
       <c r="H7">
-        <v>51.136</v>
+        <v>52.758</v>
       </c>
       <c r="I7">
-        <v>47.536</v>
+        <v>49.081</v>
       </c>
       <c r="J7">
-        <v>51.184</v>
+        <v>52.791</v>
       </c>
       <c r="K7">
-        <v>47.511</v>
+        <v>49.07</v>
       </c>
       <c r="L7">
-        <v>51.158</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="8">
@@ -666,34 +666,34 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>42.948</v>
+        <v>44.174</v>
       </c>
       <c r="D8">
-        <v>0.917</v>
+        <v>0.902</v>
       </c>
       <c r="E8">
-        <v>0.958</v>
+        <v>0.95</v>
       </c>
       <c r="F8">
         <v>0.03</v>
       </c>
       <c r="G8">
-        <v>41.081</v>
+        <v>42.321</v>
       </c>
       <c r="H8">
-        <v>44.836</v>
+        <v>46.044</v>
       </c>
       <c r="I8">
-        <v>40.93</v>
+        <v>42.238</v>
       </c>
       <c r="J8">
-        <v>44.717</v>
+        <v>45.969</v>
       </c>
       <c r="K8">
-        <v>41.19</v>
+        <v>42.387</v>
       </c>
       <c r="L8">
-        <v>44.977</v>
+        <v>46.118</v>
       </c>
     </row>
     <row r="9">
@@ -706,34 +706,34 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>37.392</v>
+        <v>38.464</v>
       </c>
       <c r="D9">
-        <v>0.755</v>
+        <v>0.751</v>
       </c>
       <c r="E9">
-        <v>0.869</v>
+        <v>0.867</v>
       </c>
       <c r="F9">
         <v>0.027</v>
       </c>
       <c r="G9">
-        <v>35.704</v>
+        <v>36.79</v>
       </c>
       <c r="H9">
-        <v>39.11</v>
+        <v>40.187</v>
       </c>
       <c r="I9">
-        <v>35.735</v>
+        <v>36.796</v>
       </c>
       <c r="J9">
-        <v>39.163</v>
+        <v>40.268</v>
       </c>
       <c r="K9">
-        <v>35.636</v>
+        <v>36.685</v>
       </c>
       <c r="L9">
-        <v>39.064</v>
+        <v>40.157</v>
       </c>
     </row>
     <row r="10">
@@ -746,34 +746,34 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>33.456</v>
+        <v>34.353</v>
       </c>
       <c r="D10">
-        <v>0.618</v>
+        <v>0.614</v>
       </c>
       <c r="E10">
-        <v>0.786</v>
+        <v>0.784</v>
       </c>
       <c r="F10">
         <v>0.025</v>
       </c>
       <c r="G10">
-        <v>31.935</v>
+        <v>32.831</v>
       </c>
       <c r="H10">
-        <v>35.016</v>
+        <v>35.904</v>
       </c>
       <c r="I10">
-        <v>31.922</v>
+        <v>32.885</v>
       </c>
       <c r="J10">
-        <v>34.982</v>
+        <v>35.89</v>
       </c>
       <c r="K10">
-        <v>31.949</v>
+        <v>32.831</v>
       </c>
       <c r="L10">
-        <v>35.009</v>
+        <v>35.835</v>
       </c>
     </row>
     <row r="11">
@@ -786,34 +786,34 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>32.202</v>
+        <v>33.07</v>
       </c>
       <c r="D11">
-        <v>0.627</v>
+        <v>0.642</v>
       </c>
       <c r="E11">
-        <v>0.792</v>
+        <v>0.801</v>
       </c>
       <c r="F11">
         <v>0.025</v>
       </c>
       <c r="G11">
-        <v>30.611</v>
+        <v>31.459</v>
       </c>
       <c r="H11">
-        <v>33.715</v>
+        <v>34.6</v>
       </c>
       <c r="I11">
-        <v>30.515</v>
+        <v>31.402</v>
       </c>
       <c r="J11">
-        <v>33.68</v>
+        <v>34.562</v>
       </c>
       <c r="K11">
-        <v>30.685</v>
+        <v>31.538</v>
       </c>
       <c r="L11">
-        <v>33.85</v>
+        <v>34.698</v>
       </c>
     </row>
     <row r="12">
@@ -826,34 +826,34 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>30.067</v>
+        <v>30.857</v>
       </c>
       <c r="D12">
-        <v>0.702</v>
+        <v>0.673</v>
       </c>
       <c r="E12">
-        <v>0.838</v>
+        <v>0.821</v>
       </c>
       <c r="F12">
         <v>0.026</v>
       </c>
       <c r="G12">
-        <v>28.509</v>
+        <v>29.337</v>
       </c>
       <c r="H12">
-        <v>31.793</v>
+        <v>32.553</v>
       </c>
       <c r="I12">
-        <v>28.347</v>
+        <v>29.247</v>
       </c>
       <c r="J12">
-        <v>31.697</v>
+        <v>32.493</v>
       </c>
       <c r="K12">
-        <v>28.522</v>
+        <v>29.309</v>
       </c>
       <c r="L12">
-        <v>31.872</v>
+        <v>32.555</v>
       </c>
     </row>
     <row r="13">
@@ -866,34 +866,34 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>31.085</v>
+        <v>31.806</v>
       </c>
       <c r="D13">
-        <v>0.668</v>
+        <v>0.666</v>
       </c>
       <c r="E13">
-        <v>0.8179999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="F13">
         <v>0.026</v>
       </c>
       <c r="G13">
-        <v>29.449</v>
+        <v>30.174</v>
       </c>
       <c r="H13">
-        <v>32.653</v>
+        <v>33.375</v>
       </c>
       <c r="I13">
-        <v>29.398</v>
+        <v>30.147</v>
       </c>
       <c r="J13">
-        <v>32.657</v>
+        <v>33.345</v>
       </c>
       <c r="K13">
-        <v>29.479</v>
+        <v>30.236</v>
       </c>
       <c r="L13">
-        <v>32.738</v>
+        <v>33.434</v>
       </c>
     </row>
     <row r="14">
@@ -906,34 +906,34 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>26.265</v>
+        <v>26.918</v>
       </c>
       <c r="D14">
-        <v>0.482</v>
+        <v>0.474</v>
       </c>
       <c r="E14">
-        <v>0.694</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="F14">
         <v>0.022</v>
       </c>
       <c r="G14">
-        <v>24.894</v>
+        <v>25.556</v>
       </c>
       <c r="H14">
-        <v>27.614</v>
+        <v>28.254</v>
       </c>
       <c r="I14">
-        <v>24.815</v>
+        <v>25.467</v>
       </c>
       <c r="J14">
-        <v>27.514</v>
+        <v>28.176</v>
       </c>
       <c r="K14">
-        <v>25.006</v>
+        <v>25.647</v>
       </c>
       <c r="L14">
-        <v>27.704</v>
+        <v>28.356</v>
       </c>
     </row>
     <row r="15">
@@ -946,34 +946,34 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>26.879</v>
+        <v>27.473</v>
       </c>
       <c r="D15">
-        <v>0.513</v>
+        <v>0.487</v>
       </c>
       <c r="E15">
-        <v>0.716</v>
+        <v>0.698</v>
       </c>
       <c r="F15">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="G15">
-        <v>25.489</v>
+        <v>26.125</v>
       </c>
       <c r="H15">
-        <v>28.296</v>
+        <v>28.861</v>
       </c>
       <c r="I15">
-        <v>25.386</v>
+        <v>25.971</v>
       </c>
       <c r="J15">
-        <v>28.22</v>
+        <v>28.816</v>
       </c>
       <c r="K15">
-        <v>25.552</v>
+        <v>26.15</v>
       </c>
       <c r="L15">
-        <v>28.385</v>
+        <v>28.994</v>
       </c>
     </row>
     <row r="16">
@@ -986,34 +986,34 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>25.065</v>
+        <v>25.709</v>
       </c>
       <c r="D16">
-        <v>0.521</v>
+        <v>0.526</v>
       </c>
       <c r="E16">
-        <v>0.722</v>
+        <v>0.725</v>
       </c>
       <c r="F16">
         <v>0.023</v>
       </c>
       <c r="G16">
-        <v>23.636</v>
+        <v>24.28</v>
       </c>
       <c r="H16">
-        <v>26.465</v>
+        <v>27.122</v>
       </c>
       <c r="I16">
-        <v>23.58</v>
+        <v>24.225</v>
       </c>
       <c r="J16">
-        <v>26.493</v>
+        <v>27.118</v>
       </c>
       <c r="K16">
-        <v>23.622</v>
+        <v>24.292</v>
       </c>
       <c r="L16">
-        <v>26.535</v>
+        <v>27.186</v>
       </c>
     </row>
     <row r="17">
@@ -1026,7 +1026,7 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>24.628</v>
+        <v>25.299</v>
       </c>
       <c r="D17">
         <v>0.49</v>
@@ -1038,22 +1038,22 @@
         <v>0.022</v>
       </c>
       <c r="G17">
-        <v>23.268</v>
+        <v>23.938</v>
       </c>
       <c r="H17">
-        <v>26.013</v>
+        <v>26.683</v>
       </c>
       <c r="I17">
-        <v>23.297</v>
+        <v>23.956</v>
       </c>
       <c r="J17">
-        <v>25.926</v>
+        <v>26.65</v>
       </c>
       <c r="K17">
-        <v>23.343</v>
+        <v>23.96</v>
       </c>
       <c r="L17">
-        <v>25.972</v>
+        <v>26.654</v>
       </c>
     </row>
     <row r="18">
@@ -1066,34 +1066,34 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>24.642</v>
+        <v>25.199</v>
       </c>
       <c r="D18">
-        <v>0.473</v>
+        <v>0.465</v>
       </c>
       <c r="E18">
-        <v>0.6879999999999999</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="F18">
         <v>0.022</v>
       </c>
       <c r="G18">
-        <v>23.311</v>
+        <v>23.882</v>
       </c>
       <c r="H18">
-        <v>26.007</v>
+        <v>26.554</v>
       </c>
       <c r="I18">
-        <v>23.328</v>
+        <v>23.905</v>
       </c>
       <c r="J18">
-        <v>25.986</v>
+        <v>26.503</v>
       </c>
       <c r="K18">
-        <v>23.315</v>
+        <v>23.914</v>
       </c>
       <c r="L18">
-        <v>25.973</v>
+        <v>26.512</v>
       </c>
     </row>
     <row r="19">
@@ -1106,34 +1106,34 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>22.336</v>
+        <v>22.885</v>
       </c>
       <c r="D19">
-        <v>0.441</v>
+        <v>0.437</v>
       </c>
       <c r="E19">
-        <v>0.664</v>
+        <v>0.661</v>
       </c>
       <c r="F19">
         <v>0.021</v>
       </c>
       <c r="G19">
-        <v>21.053</v>
+        <v>21.614</v>
       </c>
       <c r="H19">
-        <v>23.656</v>
+        <v>24.206</v>
       </c>
       <c r="I19">
-        <v>20.946</v>
+        <v>21.492</v>
       </c>
       <c r="J19">
-        <v>23.632</v>
+        <v>24.18</v>
       </c>
       <c r="K19">
-        <v>21.058</v>
+        <v>21.615</v>
       </c>
       <c r="L19">
-        <v>23.744</v>
+        <v>24.303</v>
       </c>
     </row>
     <row r="20">
@@ -1146,34 +1146,34 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>22.268</v>
+        <v>22.588</v>
       </c>
       <c r="D20">
-        <v>1.307</v>
+        <v>0.86</v>
       </c>
       <c r="E20">
-        <v>1.143</v>
+        <v>0.927</v>
       </c>
       <c r="F20">
-        <v>0.036</v>
+        <v>0.029</v>
       </c>
       <c r="G20">
-        <v>20.046</v>
+        <v>20.793</v>
       </c>
       <c r="H20">
-        <v>24.527</v>
+        <v>24.427</v>
       </c>
       <c r="I20">
-        <v>19.653</v>
+        <v>20.55</v>
       </c>
       <c r="J20">
-        <v>24.134</v>
+        <v>24.211</v>
       </c>
       <c r="K20">
-        <v>20.42</v>
+        <v>20.987</v>
       </c>
       <c r="L20">
-        <v>24.901</v>
+        <v>24.648</v>
       </c>
     </row>
     <row r="21">
@@ -1186,34 +1186,34 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>21.095</v>
+        <v>21.565</v>
       </c>
       <c r="D21">
-        <v>0.41</v>
+        <v>0.399</v>
       </c>
       <c r="E21">
-        <v>0.64</v>
+        <v>0.632</v>
       </c>
       <c r="F21">
         <v>0.02</v>
       </c>
       <c r="G21">
-        <v>19.832</v>
+        <v>20.328</v>
       </c>
       <c r="H21">
-        <v>22.342</v>
+        <v>22.805</v>
       </c>
       <c r="I21">
-        <v>19.837</v>
+        <v>20.31</v>
       </c>
       <c r="J21">
-        <v>22.327</v>
+        <v>22.814</v>
       </c>
       <c r="K21">
-        <v>19.855</v>
+        <v>20.318</v>
       </c>
       <c r="L21">
-        <v>22.345</v>
+        <v>22.821</v>
       </c>
     </row>
     <row r="22">
@@ -1226,34 +1226,34 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>20.388</v>
+        <v>20.944</v>
       </c>
       <c r="D22">
-        <v>0.421</v>
+        <v>0.418</v>
       </c>
       <c r="E22">
-        <v>0.649</v>
+        <v>0.647</v>
       </c>
       <c r="F22">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="G22">
-        <v>19.1</v>
+        <v>19.668</v>
       </c>
       <c r="H22">
-        <v>21.642</v>
+        <v>22.203</v>
       </c>
       <c r="I22">
-        <v>19.073</v>
+        <v>19.656</v>
       </c>
       <c r="J22">
-        <v>21.624</v>
+        <v>22.193</v>
       </c>
       <c r="K22">
-        <v>19.134</v>
+        <v>19.686</v>
       </c>
       <c r="L22">
-        <v>21.686</v>
+        <v>22.223</v>
       </c>
     </row>
     <row r="23">
@@ -1266,34 +1266,34 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>18.511</v>
+        <v>18.992</v>
       </c>
       <c r="D23">
-        <v>0.33</v>
+        <v>0.332</v>
       </c>
       <c r="E23">
-        <v>0.574</v>
+        <v>0.577</v>
       </c>
       <c r="F23">
         <v>0.018</v>
       </c>
       <c r="G23">
-        <v>17.358</v>
+        <v>17.838</v>
       </c>
       <c r="H23">
-        <v>19.61</v>
+        <v>20.099</v>
       </c>
       <c r="I23">
-        <v>17.35</v>
+        <v>17.812</v>
       </c>
       <c r="J23">
-        <v>19.626</v>
+        <v>20.112</v>
       </c>
       <c r="K23">
-        <v>17.369</v>
+        <v>17.849</v>
       </c>
       <c r="L23">
-        <v>19.644</v>
+        <v>20.149</v>
       </c>
     </row>
     <row r="24">
@@ -1306,34 +1306,34 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>18.213</v>
+        <v>18.769</v>
       </c>
       <c r="D24">
-        <v>0.393</v>
+        <v>0.398</v>
       </c>
       <c r="E24">
-        <v>0.627</v>
+        <v>0.631</v>
       </c>
       <c r="F24">
         <v>0.02</v>
       </c>
       <c r="G24">
-        <v>16.989</v>
+        <v>17.54</v>
       </c>
       <c r="H24">
-        <v>19.447</v>
+        <v>20.011</v>
       </c>
       <c r="I24">
-        <v>17.001</v>
+        <v>17.572</v>
       </c>
       <c r="J24">
-        <v>19.41</v>
+        <v>20</v>
       </c>
       <c r="K24">
-        <v>17.021</v>
+        <v>17.545</v>
       </c>
       <c r="L24">
-        <v>19.429</v>
+        <v>19.973</v>
       </c>
     </row>
     <row r="25">
@@ -1346,34 +1346,34 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>16.526</v>
+        <v>17.058</v>
       </c>
       <c r="D25">
-        <v>0.283</v>
+        <v>0.292</v>
       </c>
       <c r="E25">
-        <v>0.532</v>
+        <v>0.541</v>
       </c>
       <c r="F25">
         <v>0.017</v>
       </c>
       <c r="G25">
-        <v>15.473</v>
+        <v>15.988</v>
       </c>
       <c r="H25">
-        <v>17.558</v>
+        <v>18.107</v>
       </c>
       <c r="I25">
-        <v>15.438</v>
+        <v>15.959</v>
       </c>
       <c r="J25">
-        <v>17.533</v>
+        <v>18.102</v>
       </c>
       <c r="K25">
-        <v>15.509</v>
+        <v>16.003</v>
       </c>
       <c r="L25">
-        <v>17.604</v>
+        <v>18.146</v>
       </c>
     </row>
     <row r="26">
@@ -1386,34 +1386,34 @@
         <v>1</v>
       </c>
       <c r="C26">
-        <v>290.284</v>
+        <v>295.616</v>
       </c>
       <c r="D26">
-        <v>6.85</v>
+        <v>6.471</v>
       </c>
       <c r="E26">
-        <v>2.617</v>
+        <v>2.544</v>
       </c>
       <c r="F26">
-        <v>0.083</v>
+        <v>0.08</v>
       </c>
       <c r="G26">
-        <v>285.421</v>
+        <v>290.896</v>
       </c>
       <c r="H26">
-        <v>295.68</v>
+        <v>300.868</v>
       </c>
       <c r="I26">
-        <v>285.35</v>
+        <v>290.826</v>
       </c>
       <c r="J26">
-        <v>295.693</v>
+        <v>300.924</v>
       </c>
       <c r="K26">
-        <v>285.142</v>
+        <v>290.574</v>
       </c>
       <c r="L26">
-        <v>295.484</v>
+        <v>300.672</v>
       </c>
     </row>
     <row r="27">
@@ -1426,34 +1426,34 @@
         <v>2</v>
       </c>
       <c r="C27">
-        <v>187.397</v>
+        <v>191.34</v>
       </c>
       <c r="D27">
-        <v>3.812</v>
+        <v>3.751</v>
       </c>
       <c r="E27">
-        <v>1.952</v>
+        <v>1.937</v>
       </c>
       <c r="F27">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="G27">
-        <v>183.316</v>
+        <v>187.277</v>
       </c>
       <c r="H27">
-        <v>190.969</v>
+        <v>194.869</v>
       </c>
       <c r="I27">
-        <v>183.26</v>
+        <v>187.315</v>
       </c>
       <c r="J27">
-        <v>190.876</v>
+        <v>194.882</v>
       </c>
       <c r="K27">
-        <v>183.664</v>
+        <v>187.531</v>
       </c>
       <c r="L27">
-        <v>191.28</v>
+        <v>195.098</v>
       </c>
     </row>
     <row r="28">
@@ -1466,34 +1466,34 @@
         <v>3</v>
       </c>
       <c r="C28">
-        <v>123.894</v>
+        <v>127.49</v>
       </c>
       <c r="D28">
-        <v>2.941</v>
+        <v>2.798</v>
       </c>
       <c r="E28">
-        <v>1.715</v>
+        <v>1.673</v>
       </c>
       <c r="F28">
-        <v>0.054</v>
+        <v>0.053</v>
       </c>
       <c r="G28">
-        <v>120.448</v>
+        <v>124.098</v>
       </c>
       <c r="H28">
-        <v>127.171</v>
+        <v>130.655</v>
       </c>
       <c r="I28">
-        <v>120.446</v>
+        <v>124.07</v>
       </c>
       <c r="J28">
-        <v>127.184</v>
+        <v>130.675</v>
       </c>
       <c r="K28">
-        <v>120.521</v>
+        <v>124.191</v>
       </c>
       <c r="L28">
-        <v>127.259</v>
+        <v>130.796</v>
       </c>
     </row>
     <row r="29">
@@ -1506,34 +1506,34 @@
         <v>4</v>
       </c>
       <c r="C29">
-        <v>87.569</v>
+        <v>90.39400000000001</v>
       </c>
       <c r="D29">
-        <v>2.779</v>
+        <v>2.76</v>
       </c>
       <c r="E29">
-        <v>1.667</v>
+        <v>1.661</v>
       </c>
       <c r="F29">
         <v>0.053</v>
       </c>
       <c r="G29">
-        <v>84.241</v>
+        <v>87.074</v>
       </c>
       <c r="H29">
-        <v>90.77500000000001</v>
+        <v>93.587</v>
       </c>
       <c r="I29">
-        <v>83.99299999999999</v>
+        <v>86.904</v>
       </c>
       <c r="J29">
-        <v>90.521</v>
+        <v>93.39</v>
       </c>
       <c r="K29">
-        <v>84.556</v>
+        <v>87.334</v>
       </c>
       <c r="L29">
-        <v>91.084</v>
+        <v>93.81999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1546,34 +1546,34 @@
         <v>5</v>
       </c>
       <c r="C30">
-        <v>68.077</v>
+        <v>70.218</v>
       </c>
       <c r="D30">
-        <v>1.319</v>
+        <v>1.369</v>
       </c>
       <c r="E30">
-        <v>1.149</v>
+        <v>1.17</v>
       </c>
       <c r="F30">
-        <v>0.036</v>
+        <v>0.037</v>
       </c>
       <c r="G30">
-        <v>65.782</v>
+        <v>67.88200000000001</v>
       </c>
       <c r="H30">
-        <v>70.28400000000001</v>
+        <v>72.46899999999999</v>
       </c>
       <c r="I30">
-        <v>65.759</v>
+        <v>67.80200000000001</v>
       </c>
       <c r="J30">
-        <v>70.239</v>
+        <v>72.387</v>
       </c>
       <c r="K30">
-        <v>65.871</v>
+        <v>68.006</v>
       </c>
       <c r="L30">
-        <v>70.351</v>
+        <v>72.59099999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1586,34 +1586,34 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>55.067</v>
+        <v>56.836</v>
       </c>
       <c r="D31">
-        <v>1.042</v>
+        <v>1.081</v>
       </c>
       <c r="E31">
-        <v>1.021</v>
+        <v>1.04</v>
       </c>
       <c r="F31">
-        <v>0.032</v>
+        <v>0.033</v>
       </c>
       <c r="G31">
-        <v>53.146</v>
+        <v>54.876</v>
       </c>
       <c r="H31">
-        <v>57.148</v>
+        <v>58.952</v>
       </c>
       <c r="I31">
-        <v>53.2</v>
+        <v>54.874</v>
       </c>
       <c r="J31">
-        <v>57.188</v>
+        <v>59.028</v>
       </c>
       <c r="K31">
-        <v>53.027</v>
+        <v>54.721</v>
       </c>
       <c r="L31">
-        <v>57.014</v>
+        <v>58.875</v>
       </c>
     </row>
     <row r="32">
@@ -1626,10 +1626,10 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <v>47.926</v>
+        <v>49.298</v>
       </c>
       <c r="D32">
-        <v>1.003</v>
+        <v>1.004</v>
       </c>
       <c r="E32">
         <v>1.002</v>
@@ -1638,22 +1638,22 @@
         <v>0.032</v>
       </c>
       <c r="G32">
-        <v>46.045</v>
+        <v>47.407</v>
       </c>
       <c r="H32">
-        <v>49.971</v>
+        <v>51.334</v>
       </c>
       <c r="I32">
-        <v>46.023</v>
+        <v>47.414</v>
       </c>
       <c r="J32">
-        <v>49.927</v>
+        <v>51.277</v>
       </c>
       <c r="K32">
-        <v>46.007</v>
+        <v>47.391</v>
       </c>
       <c r="L32">
-        <v>49.911</v>
+        <v>51.255</v>
       </c>
     </row>
     <row r="33">
@@ -1666,34 +1666,34 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <v>41.748</v>
+        <v>42.955</v>
       </c>
       <c r="D33">
-        <v>0.926</v>
+        <v>0.928</v>
       </c>
       <c r="E33">
-        <v>0.962</v>
+        <v>0.964</v>
       </c>
       <c r="F33">
         <v>0.03</v>
       </c>
       <c r="G33">
-        <v>39.896</v>
+        <v>41.092</v>
       </c>
       <c r="H33">
-        <v>43.667</v>
+        <v>44.869</v>
       </c>
       <c r="I33">
-        <v>39.851</v>
+        <v>41.033</v>
       </c>
       <c r="J33">
-        <v>43.517</v>
+        <v>44.763</v>
       </c>
       <c r="K33">
-        <v>40.012</v>
+        <v>41.171</v>
       </c>
       <c r="L33">
-        <v>43.678</v>
+        <v>44.902</v>
       </c>
     </row>
     <row r="34">
@@ -1706,34 +1706,34 @@
         <v>9</v>
       </c>
       <c r="C34">
-        <v>37.389</v>
+        <v>38.388</v>
       </c>
       <c r="D34">
-        <v>0.789</v>
+        <v>0.779</v>
       </c>
       <c r="E34">
-        <v>0.888</v>
+        <v>0.882</v>
       </c>
       <c r="F34">
         <v>0.028</v>
       </c>
       <c r="G34">
-        <v>35.614</v>
+        <v>36.625</v>
       </c>
       <c r="H34">
-        <v>39.096</v>
+        <v>40.084</v>
       </c>
       <c r="I34">
-        <v>35.694</v>
+        <v>36.743</v>
       </c>
       <c r="J34">
-        <v>39.103</v>
+        <v>40.151</v>
       </c>
       <c r="K34">
-        <v>35.64</v>
+        <v>36.591</v>
       </c>
       <c r="L34">
-        <v>39.05</v>
+        <v>39.999</v>
       </c>
     </row>
     <row r="35">
@@ -1746,34 +1746,34 @@
         <v>10</v>
       </c>
       <c r="C35">
-        <v>35.92</v>
+        <v>36.886</v>
       </c>
       <c r="D35">
-        <v>0.732</v>
+        <v>0.751</v>
       </c>
       <c r="E35">
-        <v>0.856</v>
+        <v>0.866</v>
       </c>
       <c r="F35">
         <v>0.027</v>
       </c>
       <c r="G35">
-        <v>34.281</v>
+        <v>35.23</v>
       </c>
       <c r="H35">
-        <v>37.635</v>
+        <v>38.627</v>
       </c>
       <c r="I35">
-        <v>34.185</v>
+        <v>35.202</v>
       </c>
       <c r="J35">
-        <v>37.591</v>
+        <v>38.59</v>
       </c>
       <c r="K35">
-        <v>34.287</v>
+        <v>35.225</v>
       </c>
       <c r="L35">
-        <v>37.693</v>
+        <v>38.613</v>
       </c>
     </row>
     <row r="36">
@@ -1786,34 +1786,34 @@
         <v>11</v>
       </c>
       <c r="C36">
-        <v>33.59</v>
+        <v>34.472</v>
       </c>
       <c r="D36">
-        <v>0.799</v>
+        <v>0.77</v>
       </c>
       <c r="E36">
-        <v>0.894</v>
+        <v>0.877</v>
       </c>
       <c r="F36">
         <v>0.028</v>
       </c>
       <c r="G36">
-        <v>31.905</v>
+        <v>32.823</v>
       </c>
       <c r="H36">
-        <v>35.409</v>
+        <v>36.262</v>
       </c>
       <c r="I36">
-        <v>31.788</v>
+        <v>32.653</v>
       </c>
       <c r="J36">
-        <v>35.433</v>
+        <v>36.228</v>
       </c>
       <c r="K36">
-        <v>31.814</v>
+        <v>32.787</v>
       </c>
       <c r="L36">
-        <v>35.459</v>
+        <v>36.362</v>
       </c>
     </row>
     <row r="37">
@@ -1826,34 +1826,34 @@
         <v>12</v>
       </c>
       <c r="C37">
-        <v>34.704</v>
+        <v>35.508</v>
       </c>
       <c r="D37">
-        <v>0.76</v>
+        <v>0.754</v>
       </c>
       <c r="E37">
-        <v>0.872</v>
+        <v>0.868</v>
       </c>
       <c r="F37">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="G37">
-        <v>32.976</v>
+        <v>33.792</v>
       </c>
       <c r="H37">
-        <v>36.393</v>
+        <v>37.195</v>
       </c>
       <c r="I37">
-        <v>32.837</v>
+        <v>33.736</v>
       </c>
       <c r="J37">
-        <v>36.313</v>
+        <v>37.139</v>
       </c>
       <c r="K37">
-        <v>33.075</v>
+        <v>33.863</v>
       </c>
       <c r="L37">
-        <v>36.551</v>
+        <v>37.266</v>
       </c>
     </row>
     <row r="38">
@@ -1866,34 +1866,34 @@
         <v>13</v>
       </c>
       <c r="C38">
-        <v>29.274</v>
+        <v>30.006</v>
       </c>
       <c r="D38">
-        <v>0.58</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="E38">
-        <v>0.762</v>
+        <v>0.752</v>
       </c>
       <c r="F38">
         <v>0.024</v>
       </c>
       <c r="G38">
-        <v>27.883</v>
+        <v>28.625</v>
       </c>
       <c r="H38">
-        <v>30.868</v>
+        <v>31.573</v>
       </c>
       <c r="I38">
-        <v>27.834</v>
+        <v>28.568</v>
       </c>
       <c r="J38">
-        <v>30.901</v>
+        <v>31.617</v>
       </c>
       <c r="K38">
-        <v>27.748</v>
+        <v>28.488</v>
       </c>
       <c r="L38">
-        <v>30.815</v>
+        <v>31.537</v>
       </c>
     </row>
     <row r="39">
@@ -1906,34 +1906,34 @@
         <v>14</v>
       </c>
       <c r="C39">
-        <v>29.973</v>
+        <v>30.641</v>
       </c>
       <c r="D39">
-        <v>0.671</v>
+        <v>0.627</v>
       </c>
       <c r="E39">
-        <v>0.819</v>
+        <v>0.792</v>
       </c>
       <c r="F39">
-        <v>0.026</v>
+        <v>0.025</v>
       </c>
       <c r="G39">
-        <v>28.469</v>
+        <v>29.189</v>
       </c>
       <c r="H39">
-        <v>31.68</v>
+        <v>32.292</v>
       </c>
       <c r="I39">
-        <v>28.306</v>
+        <v>29.085</v>
       </c>
       <c r="J39">
-        <v>31.65</v>
+        <v>32.252</v>
       </c>
       <c r="K39">
-        <v>28.397</v>
+        <v>29.129</v>
       </c>
       <c r="L39">
-        <v>31.741</v>
+        <v>32.296</v>
       </c>
     </row>
     <row r="40">
@@ -1946,34 +1946,34 @@
         <v>15</v>
       </c>
       <c r="C40">
-        <v>27.976</v>
+        <v>28.701</v>
       </c>
       <c r="D40">
-        <v>0.583</v>
+        <v>0.595</v>
       </c>
       <c r="E40">
-        <v>0.764</v>
+        <v>0.772</v>
       </c>
       <c r="F40">
         <v>0.024</v>
       </c>
       <c r="G40">
-        <v>26.491</v>
+        <v>27.198</v>
       </c>
       <c r="H40">
-        <v>29.485</v>
+        <v>30.223</v>
       </c>
       <c r="I40">
-        <v>26.407</v>
+        <v>27.122</v>
       </c>
       <c r="J40">
-        <v>29.457</v>
+        <v>30.203</v>
       </c>
       <c r="K40">
-        <v>26.507</v>
+        <v>27.208</v>
       </c>
       <c r="L40">
-        <v>29.557</v>
+        <v>30.289</v>
       </c>
     </row>
     <row r="41">
@@ -1986,34 +1986,34 @@
         <v>16</v>
       </c>
       <c r="C41">
-        <v>27.536</v>
+        <v>28.285</v>
       </c>
       <c r="D41">
-        <v>0.596</v>
+        <v>0.595</v>
       </c>
       <c r="E41">
-        <v>0.772</v>
+        <v>0.771</v>
       </c>
       <c r="F41">
         <v>0.024</v>
       </c>
       <c r="G41">
-        <v>25.97</v>
+        <v>26.72</v>
       </c>
       <c r="H41">
-        <v>28.995</v>
+        <v>29.743</v>
       </c>
       <c r="I41">
-        <v>25.932</v>
+        <v>26.699</v>
       </c>
       <c r="J41">
-        <v>28.935</v>
+        <v>29.676</v>
       </c>
       <c r="K41">
-        <v>26.084</v>
+        <v>26.841</v>
       </c>
       <c r="L41">
-        <v>29.087</v>
+        <v>29.818</v>
       </c>
     </row>
     <row r="42">
@@ -2026,34 +2026,34 @@
         <v>17</v>
       </c>
       <c r="C42">
-        <v>27.504</v>
+        <v>28.13</v>
       </c>
       <c r="D42">
-        <v>0.592</v>
+        <v>0.585</v>
       </c>
       <c r="E42">
-        <v>0.769</v>
+        <v>0.765</v>
       </c>
       <c r="F42">
         <v>0.024</v>
       </c>
       <c r="G42">
-        <v>26.043</v>
+        <v>26.673</v>
       </c>
       <c r="H42">
-        <v>29.059</v>
+        <v>29.671</v>
       </c>
       <c r="I42">
-        <v>26.072</v>
+        <v>26.715</v>
       </c>
       <c r="J42">
-        <v>29.013</v>
+        <v>29.612</v>
       </c>
       <c r="K42">
-        <v>26.042</v>
+        <v>26.69</v>
       </c>
       <c r="L42">
-        <v>28.983</v>
+        <v>29.587</v>
       </c>
     </row>
     <row r="43">
@@ -2066,34 +2066,34 @@
         <v>18</v>
       </c>
       <c r="C43">
-        <v>24.959</v>
+        <v>25.578</v>
       </c>
       <c r="D43">
-        <v>0.526</v>
+        <v>0.527</v>
       </c>
       <c r="E43">
-        <v>0.725</v>
+        <v>0.726</v>
       </c>
       <c r="F43">
         <v>0.023</v>
       </c>
       <c r="G43">
-        <v>23.527</v>
+        <v>24.14</v>
       </c>
       <c r="H43">
-        <v>26.368</v>
+        <v>26.984</v>
       </c>
       <c r="I43">
-        <v>23.491</v>
+        <v>24.091</v>
       </c>
       <c r="J43">
-        <v>26.347</v>
+        <v>26.935</v>
       </c>
       <c r="K43">
-        <v>23.559</v>
+        <v>24.205</v>
       </c>
       <c r="L43">
-        <v>26.416</v>
+        <v>27.049</v>
       </c>
     </row>
     <row r="44">
@@ -2106,34 +2106,34 @@
         <v>19</v>
       </c>
       <c r="C44">
-        <v>24.834</v>
+        <v>25.204</v>
       </c>
       <c r="D44">
-        <v>1.448</v>
+        <v>0.964</v>
       </c>
       <c r="E44">
-        <v>1.203</v>
+        <v>0.982</v>
       </c>
       <c r="F44">
-        <v>0.038</v>
+        <v>0.031</v>
       </c>
       <c r="G44">
-        <v>22.562</v>
+        <v>23.345</v>
       </c>
       <c r="H44">
-        <v>27.279</v>
+        <v>27.194</v>
       </c>
       <c r="I44">
-        <v>22.28</v>
+        <v>23.176</v>
       </c>
       <c r="J44">
-        <v>26.944</v>
+        <v>27.031</v>
       </c>
       <c r="K44">
-        <v>22.811</v>
+        <v>23.443</v>
       </c>
       <c r="L44">
-        <v>27.474</v>
+        <v>27.297</v>
       </c>
     </row>
     <row r="45">
@@ -2146,34 +2146,34 @@
         <v>20</v>
       </c>
       <c r="C45">
-        <v>23.567</v>
+        <v>24.095</v>
       </c>
       <c r="D45">
-        <v>0.524</v>
+        <v>0.506</v>
       </c>
       <c r="E45">
-        <v>0.724</v>
+        <v>0.711</v>
       </c>
       <c r="F45">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="G45">
-        <v>22.119</v>
+        <v>22.676</v>
       </c>
       <c r="H45">
-        <v>24.957</v>
+        <v>25.464</v>
       </c>
       <c r="I45">
-        <v>22.115</v>
+        <v>22.67</v>
       </c>
       <c r="J45">
-        <v>24.881</v>
+        <v>25.418</v>
       </c>
       <c r="K45">
-        <v>22.224</v>
+        <v>22.747</v>
       </c>
       <c r="L45">
-        <v>24.99</v>
+        <v>25.495</v>
       </c>
     </row>
     <row r="46">
@@ -2186,34 +2186,34 @@
         <v>21</v>
       </c>
       <c r="C46">
-        <v>22.774</v>
+        <v>23.398</v>
       </c>
       <c r="D46">
-        <v>0.518</v>
+        <v>0.513</v>
       </c>
       <c r="E46">
-        <v>0.72</v>
+        <v>0.716</v>
       </c>
       <c r="F46">
         <v>0.023</v>
       </c>
       <c r="G46">
-        <v>21.331</v>
+        <v>21.965</v>
       </c>
       <c r="H46">
-        <v>24.153</v>
+        <v>24.773</v>
       </c>
       <c r="I46">
-        <v>21.282</v>
+        <v>21.929</v>
       </c>
       <c r="J46">
-        <v>24.085</v>
+        <v>24.718</v>
       </c>
       <c r="K46">
-        <v>21.431</v>
+        <v>22.05</v>
       </c>
       <c r="L46">
-        <v>24.234</v>
+        <v>24.839</v>
       </c>
     </row>
     <row r="47">
@@ -2226,34 +2226,34 @@
         <v>22</v>
       </c>
       <c r="C47">
-        <v>20.626</v>
+        <v>21.165</v>
       </c>
       <c r="D47">
-        <v>0.428</v>
+        <v>0.43</v>
       </c>
       <c r="E47">
-        <v>0.654</v>
+        <v>0.655</v>
       </c>
       <c r="F47">
         <v>0.021</v>
       </c>
       <c r="G47">
-        <v>19.404</v>
+        <v>19.941</v>
       </c>
       <c r="H47">
-        <v>21.968</v>
+        <v>22.511</v>
       </c>
       <c r="I47">
-        <v>19.473</v>
+        <v>20.01</v>
       </c>
       <c r="J47">
-        <v>21.935</v>
+        <v>22.48</v>
       </c>
       <c r="K47">
-        <v>19.377</v>
+        <v>19.911</v>
       </c>
       <c r="L47">
-        <v>21.84</v>
+        <v>22.381</v>
       </c>
     </row>
     <row r="48">
@@ -2266,34 +2266,34 @@
         <v>23</v>
       </c>
       <c r="C48">
-        <v>20.365</v>
+        <v>20.988</v>
       </c>
       <c r="D48">
-        <v>0.49</v>
+        <v>0.492</v>
       </c>
       <c r="E48">
-        <v>0.7</v>
+        <v>0.702</v>
       </c>
       <c r="F48">
         <v>0.022</v>
       </c>
       <c r="G48">
-        <v>18.945</v>
+        <v>19.564</v>
       </c>
       <c r="H48">
-        <v>21.69</v>
+        <v>22.314</v>
       </c>
       <c r="I48">
-        <v>18.941</v>
+        <v>19.55</v>
       </c>
       <c r="J48">
-        <v>21.656</v>
+        <v>22.224</v>
       </c>
       <c r="K48">
-        <v>19.027</v>
+        <v>19.703</v>
       </c>
       <c r="L48">
-        <v>21.742</v>
+        <v>22.377</v>
       </c>
     </row>
     <row r="49">
@@ -2306,34 +2306,34 @@
         <v>24</v>
       </c>
       <c r="C49">
-        <v>18.464</v>
+        <v>19.056</v>
       </c>
       <c r="D49">
-        <v>0.347</v>
+        <v>0.352</v>
       </c>
       <c r="E49">
-        <v>0.589</v>
+        <v>0.593</v>
       </c>
       <c r="F49">
         <v>0.019</v>
       </c>
       <c r="G49">
-        <v>17.281</v>
+        <v>17.867</v>
       </c>
       <c r="H49">
-        <v>19.589</v>
+        <v>20.192</v>
       </c>
       <c r="I49">
-        <v>17.16</v>
+        <v>17.708</v>
       </c>
       <c r="J49">
-        <v>19.585</v>
+        <v>20.165</v>
       </c>
       <c r="K49">
-        <v>17.314</v>
+        <v>17.92</v>
       </c>
       <c r="L49">
-        <v>19.739</v>
+        <v>20.377</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Monthly/monthly_combined_bootstrap_summary_costs_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Monthly/monthly_combined_bootstrap_summary_costs_SOURCE.xlsx
@@ -426,34 +426,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>264.802</v>
+        <v>252.558</v>
       </c>
       <c r="D2">
-        <v>6.013</v>
+        <v>5.283</v>
       </c>
       <c r="E2">
-        <v>2.452</v>
+        <v>2.299</v>
       </c>
       <c r="F2">
-        <v>0.078</v>
+        <v>0.073</v>
       </c>
       <c r="G2">
-        <v>260.068</v>
+        <v>248.116</v>
       </c>
       <c r="H2">
-        <v>269.68</v>
+        <v>257.126</v>
       </c>
       <c r="I2">
-        <v>260.436</v>
+        <v>248.035</v>
       </c>
       <c r="J2">
-        <v>269.786</v>
+        <v>257.141</v>
       </c>
       <c r="K2">
-        <v>259.889</v>
+        <v>248.038</v>
       </c>
       <c r="L2">
-        <v>269.24</v>
+        <v>257.144</v>
       </c>
     </row>
     <row r="3">
@@ -466,34 +466,34 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>171.221</v>
+        <v>179.61</v>
       </c>
       <c r="D3">
-        <v>3.485</v>
+        <v>4.272</v>
       </c>
       <c r="E3">
-        <v>1.867</v>
+        <v>2.067</v>
       </c>
       <c r="F3">
-        <v>0.059</v>
+        <v>0.065</v>
       </c>
       <c r="G3">
-        <v>167.564</v>
+        <v>175.556</v>
       </c>
       <c r="H3">
-        <v>174.882</v>
+        <v>183.658</v>
       </c>
       <c r="I3">
-        <v>167.525</v>
+        <v>175.544</v>
       </c>
       <c r="J3">
-        <v>174.859</v>
+        <v>183.622</v>
       </c>
       <c r="K3">
-        <v>167.585</v>
+        <v>175.595</v>
       </c>
       <c r="L3">
-        <v>174.919</v>
+        <v>183.673</v>
       </c>
     </row>
     <row r="4">
@@ -506,34 +506,34 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>114.154</v>
+        <v>122.817</v>
       </c>
       <c r="D4">
-        <v>2.293</v>
+        <v>2.524</v>
       </c>
       <c r="E4">
-        <v>1.514</v>
+        <v>1.589</v>
       </c>
       <c r="F4">
-        <v>0.048</v>
+        <v>0.05</v>
       </c>
       <c r="G4">
-        <v>111.106</v>
+        <v>119.617</v>
       </c>
       <c r="H4">
-        <v>117.042</v>
+        <v>125.844</v>
       </c>
       <c r="I4">
-        <v>111.077</v>
+        <v>119.643</v>
       </c>
       <c r="J4">
-        <v>116.973</v>
+        <v>125.693</v>
       </c>
       <c r="K4">
-        <v>111.255</v>
+        <v>119.855</v>
       </c>
       <c r="L4">
-        <v>117.151</v>
+        <v>125.905</v>
       </c>
     </row>
     <row r="5">
@@ -546,34 +546,34 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>81.008</v>
+        <v>85.992</v>
       </c>
       <c r="D5">
-        <v>2.391</v>
+        <v>1.855</v>
       </c>
       <c r="E5">
-        <v>1.546</v>
+        <v>1.362</v>
       </c>
       <c r="F5">
-        <v>0.049</v>
+        <v>0.043</v>
       </c>
       <c r="G5">
-        <v>77.797</v>
+        <v>83.224</v>
       </c>
       <c r="H5">
-        <v>83.858</v>
+        <v>88.563</v>
       </c>
       <c r="I5">
-        <v>77.35599999999999</v>
+        <v>83.13200000000001</v>
       </c>
       <c r="J5">
-        <v>83.64100000000001</v>
+        <v>88.504</v>
       </c>
       <c r="K5">
-        <v>78.194</v>
+        <v>83.381</v>
       </c>
       <c r="L5">
-        <v>84.48</v>
+        <v>88.753</v>
       </c>
     </row>
     <row r="6">
@@ -586,34 +586,34 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>62.851</v>
+        <v>65.80800000000001</v>
       </c>
       <c r="D6">
-        <v>1.043</v>
+        <v>1.221</v>
       </c>
       <c r="E6">
-        <v>1.021</v>
+        <v>1.105</v>
       </c>
       <c r="F6">
-        <v>0.032</v>
+        <v>0.035</v>
       </c>
       <c r="G6">
-        <v>60.867</v>
+        <v>63.609</v>
       </c>
       <c r="H6">
-        <v>64.871</v>
+        <v>67.94</v>
       </c>
       <c r="I6">
-        <v>60.801</v>
+        <v>63.564</v>
       </c>
       <c r="J6">
-        <v>64.843</v>
+        <v>67.836</v>
       </c>
       <c r="K6">
-        <v>60.877</v>
+        <v>63.746</v>
       </c>
       <c r="L6">
-        <v>64.91800000000001</v>
+        <v>68.017</v>
       </c>
     </row>
     <row r="7">
@@ -626,34 +626,34 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>50.917</v>
+        <v>52.254</v>
       </c>
       <c r="D7">
-        <v>0.857</v>
+        <v>0.93</v>
       </c>
       <c r="E7">
-        <v>0.926</v>
+        <v>0.964</v>
       </c>
       <c r="F7">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="G7">
-        <v>49.13</v>
+        <v>50.377</v>
       </c>
       <c r="H7">
-        <v>52.758</v>
+        <v>54.156</v>
       </c>
       <c r="I7">
-        <v>49.081</v>
+        <v>50.38</v>
       </c>
       <c r="J7">
-        <v>52.791</v>
+        <v>54.123</v>
       </c>
       <c r="K7">
-        <v>49.07</v>
+        <v>50.397</v>
       </c>
       <c r="L7">
-        <v>52.78</v>
+        <v>54.14</v>
       </c>
     </row>
     <row r="8">
@@ -666,34 +666,34 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>44.174</v>
+        <v>43.939</v>
       </c>
       <c r="D8">
-        <v>0.902</v>
+        <v>0.87</v>
       </c>
       <c r="E8">
-        <v>0.95</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="F8">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="G8">
-        <v>42.321</v>
+        <v>42.103</v>
       </c>
       <c r="H8">
-        <v>46.044</v>
+        <v>45.758</v>
       </c>
       <c r="I8">
-        <v>42.238</v>
+        <v>42.016</v>
       </c>
       <c r="J8">
-        <v>45.969</v>
+        <v>45.736</v>
       </c>
       <c r="K8">
-        <v>42.387</v>
+        <v>42.133</v>
       </c>
       <c r="L8">
-        <v>46.118</v>
+        <v>45.853</v>
       </c>
     </row>
     <row r="9">
@@ -706,34 +706,34 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>38.464</v>
+        <v>37.318</v>
       </c>
       <c r="D9">
-        <v>0.751</v>
+        <v>0.671</v>
       </c>
       <c r="E9">
-        <v>0.867</v>
+        <v>0.819</v>
       </c>
       <c r="F9">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
       <c r="G9">
-        <v>36.79</v>
+        <v>35.729</v>
       </c>
       <c r="H9">
-        <v>40.187</v>
+        <v>38.941</v>
       </c>
       <c r="I9">
-        <v>36.796</v>
+        <v>35.741</v>
       </c>
       <c r="J9">
-        <v>40.268</v>
+        <v>38.956</v>
       </c>
       <c r="K9">
-        <v>36.685</v>
+        <v>35.698</v>
       </c>
       <c r="L9">
-        <v>40.157</v>
+        <v>38.913</v>
       </c>
     </row>
     <row r="10">
@@ -746,34 +746,34 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>34.353</v>
+        <v>33.54</v>
       </c>
       <c r="D10">
-        <v>0.614</v>
+        <v>0.55</v>
       </c>
       <c r="E10">
-        <v>0.784</v>
+        <v>0.742</v>
       </c>
       <c r="F10">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
       <c r="G10">
-        <v>32.831</v>
+        <v>32.102</v>
       </c>
       <c r="H10">
-        <v>35.904</v>
+        <v>35.011</v>
       </c>
       <c r="I10">
-        <v>32.885</v>
+        <v>32.076</v>
       </c>
       <c r="J10">
-        <v>35.89</v>
+        <v>34.952</v>
       </c>
       <c r="K10">
-        <v>32.831</v>
+        <v>32.145</v>
       </c>
       <c r="L10">
-        <v>35.835</v>
+        <v>35.021</v>
       </c>
     </row>
     <row r="11">
@@ -786,34 +786,34 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>33.07</v>
+        <v>31.793</v>
       </c>
       <c r="D11">
-        <v>0.642</v>
+        <v>0.604</v>
       </c>
       <c r="E11">
-        <v>0.801</v>
+        <v>0.777</v>
       </c>
       <c r="F11">
         <v>0.025</v>
       </c>
       <c r="G11">
-        <v>31.459</v>
+        <v>30.237</v>
       </c>
       <c r="H11">
-        <v>34.6</v>
+        <v>33.285</v>
       </c>
       <c r="I11">
-        <v>31.402</v>
+        <v>30.163</v>
       </c>
       <c r="J11">
-        <v>34.562</v>
+        <v>33.282</v>
       </c>
       <c r="K11">
-        <v>31.538</v>
+        <v>30.272</v>
       </c>
       <c r="L11">
-        <v>34.698</v>
+        <v>33.391</v>
       </c>
     </row>
     <row r="12">
@@ -826,34 +826,34 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>30.857</v>
+        <v>29.891</v>
       </c>
       <c r="D12">
-        <v>0.673</v>
+        <v>0.722</v>
       </c>
       <c r="E12">
-        <v>0.821</v>
+        <v>0.85</v>
       </c>
       <c r="F12">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="G12">
-        <v>29.337</v>
+        <v>28.313</v>
       </c>
       <c r="H12">
-        <v>32.553</v>
+        <v>31.644</v>
       </c>
       <c r="I12">
-        <v>29.247</v>
+        <v>28.282</v>
       </c>
       <c r="J12">
-        <v>32.493</v>
+        <v>31.567</v>
       </c>
       <c r="K12">
-        <v>29.309</v>
+        <v>28.302</v>
       </c>
       <c r="L12">
-        <v>32.555</v>
+        <v>31.587</v>
       </c>
     </row>
     <row r="13">
@@ -866,34 +866,34 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>31.806</v>
+        <v>30.569</v>
       </c>
       <c r="D13">
-        <v>0.666</v>
+        <v>0.61</v>
       </c>
       <c r="E13">
-        <v>0.8159999999999999</v>
+        <v>0.781</v>
       </c>
       <c r="F13">
-        <v>0.026</v>
+        <v>0.025</v>
       </c>
       <c r="G13">
-        <v>30.174</v>
+        <v>28.988</v>
       </c>
       <c r="H13">
-        <v>33.375</v>
+        <v>32.05</v>
       </c>
       <c r="I13">
-        <v>30.147</v>
+        <v>28.897</v>
       </c>
       <c r="J13">
-        <v>33.345</v>
+        <v>31.971</v>
       </c>
       <c r="K13">
-        <v>30.236</v>
+        <v>29.117</v>
       </c>
       <c r="L13">
-        <v>33.434</v>
+        <v>32.192</v>
       </c>
     </row>
     <row r="14">
@@ -906,34 +906,34 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>26.918</v>
+        <v>25.883</v>
       </c>
       <c r="D14">
-        <v>0.474</v>
+        <v>0.421</v>
       </c>
       <c r="E14">
-        <v>0.6879999999999999</v>
+        <v>0.649</v>
       </c>
       <c r="F14">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="G14">
-        <v>25.556</v>
+        <v>24.615</v>
       </c>
       <c r="H14">
-        <v>28.254</v>
+        <v>27.159</v>
       </c>
       <c r="I14">
-        <v>25.467</v>
+        <v>24.68</v>
       </c>
       <c r="J14">
-        <v>28.176</v>
+        <v>27.197</v>
       </c>
       <c r="K14">
-        <v>25.647</v>
+        <v>24.573</v>
       </c>
       <c r="L14">
-        <v>28.356</v>
+        <v>27.089</v>
       </c>
     </row>
     <row r="15">
@@ -946,34 +946,34 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>27.473</v>
+        <v>25.993</v>
       </c>
       <c r="D15">
-        <v>0.487</v>
+        <v>0.416</v>
       </c>
       <c r="E15">
-        <v>0.698</v>
+        <v>0.645</v>
       </c>
       <c r="F15">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="G15">
-        <v>26.125</v>
+        <v>24.775</v>
       </c>
       <c r="H15">
-        <v>28.861</v>
+        <v>27.302</v>
       </c>
       <c r="I15">
-        <v>25.971</v>
+        <v>24.673</v>
       </c>
       <c r="J15">
-        <v>28.816</v>
+        <v>27.343</v>
       </c>
       <c r="K15">
-        <v>26.15</v>
+        <v>24.689</v>
       </c>
       <c r="L15">
-        <v>28.994</v>
+        <v>27.359</v>
       </c>
     </row>
     <row r="16">
@@ -986,34 +986,34 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>25.709</v>
+        <v>24.673</v>
       </c>
       <c r="D16">
-        <v>0.526</v>
+        <v>0.449</v>
       </c>
       <c r="E16">
-        <v>0.725</v>
+        <v>0.67</v>
       </c>
       <c r="F16">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
       <c r="G16">
-        <v>24.28</v>
+        <v>23.362</v>
       </c>
       <c r="H16">
-        <v>27.122</v>
+        <v>25.988</v>
       </c>
       <c r="I16">
-        <v>24.225</v>
+        <v>23.259</v>
       </c>
       <c r="J16">
-        <v>27.118</v>
+        <v>25.92</v>
       </c>
       <c r="K16">
-        <v>24.292</v>
+        <v>23.427</v>
       </c>
       <c r="L16">
-        <v>27.186</v>
+        <v>26.089</v>
       </c>
     </row>
     <row r="17">
@@ -1026,34 +1026,34 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>25.299</v>
+        <v>24.272</v>
       </c>
       <c r="D17">
-        <v>0.49</v>
+        <v>0.496</v>
       </c>
       <c r="E17">
-        <v>0.7</v>
+        <v>0.704</v>
       </c>
       <c r="F17">
         <v>0.022</v>
       </c>
       <c r="G17">
-        <v>23.938</v>
+        <v>22.91</v>
       </c>
       <c r="H17">
-        <v>26.683</v>
+        <v>25.67</v>
       </c>
       <c r="I17">
-        <v>23.956</v>
+        <v>22.885</v>
       </c>
       <c r="J17">
-        <v>26.65</v>
+        <v>25.612</v>
       </c>
       <c r="K17">
-        <v>23.96</v>
+        <v>22.951</v>
       </c>
       <c r="L17">
-        <v>26.654</v>
+        <v>25.677</v>
       </c>
     </row>
     <row r="18">
@@ -1066,34 +1066,34 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>25.199</v>
+        <v>23.793</v>
       </c>
       <c r="D18">
-        <v>0.465</v>
+        <v>0.426</v>
       </c>
       <c r="E18">
-        <v>0.6820000000000001</v>
+        <v>0.652</v>
       </c>
       <c r="F18">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="G18">
-        <v>23.882</v>
+        <v>22.549</v>
       </c>
       <c r="H18">
-        <v>26.554</v>
+        <v>25.106</v>
       </c>
       <c r="I18">
-        <v>23.905</v>
+        <v>22.517</v>
       </c>
       <c r="J18">
-        <v>26.503</v>
+        <v>25.055</v>
       </c>
       <c r="K18">
-        <v>23.914</v>
+        <v>22.565</v>
       </c>
       <c r="L18">
-        <v>26.512</v>
+        <v>25.104</v>
       </c>
     </row>
     <row r="19">
@@ -1106,34 +1106,34 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>22.885</v>
+        <v>21.954</v>
       </c>
       <c r="D19">
-        <v>0.437</v>
+        <v>0.405</v>
       </c>
       <c r="E19">
-        <v>0.661</v>
+        <v>0.637</v>
       </c>
       <c r="F19">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="G19">
-        <v>21.614</v>
+        <v>20.704</v>
       </c>
       <c r="H19">
-        <v>24.206</v>
+        <v>23.2</v>
       </c>
       <c r="I19">
-        <v>21.492</v>
+        <v>20.641</v>
       </c>
       <c r="J19">
-        <v>24.18</v>
+        <v>23.192</v>
       </c>
       <c r="K19">
-        <v>21.615</v>
+        <v>20.714</v>
       </c>
       <c r="L19">
-        <v>24.303</v>
+        <v>23.265</v>
       </c>
     </row>
     <row r="20">
@@ -1146,34 +1146,34 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>22.588</v>
+        <v>21.504</v>
       </c>
       <c r="D20">
-        <v>0.86</v>
+        <v>0.421</v>
       </c>
       <c r="E20">
-        <v>0.927</v>
+        <v>0.649</v>
       </c>
       <c r="F20">
-        <v>0.029</v>
+        <v>0.021</v>
       </c>
       <c r="G20">
-        <v>20.793</v>
+        <v>20.248</v>
       </c>
       <c r="H20">
-        <v>24.427</v>
+        <v>22.791</v>
       </c>
       <c r="I20">
-        <v>20.55</v>
+        <v>20.21</v>
       </c>
       <c r="J20">
-        <v>24.211</v>
+        <v>22.765</v>
       </c>
       <c r="K20">
-        <v>20.987</v>
+        <v>20.258</v>
       </c>
       <c r="L20">
-        <v>24.648</v>
+        <v>22.813</v>
       </c>
     </row>
     <row r="21">
@@ -1186,34 +1186,34 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>21.565</v>
+        <v>20.929</v>
       </c>
       <c r="D21">
-        <v>0.399</v>
+        <v>0.381</v>
       </c>
       <c r="E21">
-        <v>0.632</v>
+        <v>0.618</v>
       </c>
       <c r="F21">
         <v>0.02</v>
       </c>
       <c r="G21">
-        <v>20.328</v>
+        <v>19.71</v>
       </c>
       <c r="H21">
-        <v>22.805</v>
+        <v>22.131</v>
       </c>
       <c r="I21">
-        <v>20.31</v>
+        <v>19.676</v>
       </c>
       <c r="J21">
-        <v>22.814</v>
+        <v>22.131</v>
       </c>
       <c r="K21">
-        <v>20.318</v>
+        <v>19.719</v>
       </c>
       <c r="L21">
-        <v>22.821</v>
+        <v>22.174</v>
       </c>
     </row>
     <row r="22">
@@ -1226,34 +1226,34 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>20.944</v>
+        <v>20.452</v>
       </c>
       <c r="D22">
-        <v>0.418</v>
+        <v>0.396</v>
       </c>
       <c r="E22">
-        <v>0.647</v>
+        <v>0.63</v>
       </c>
       <c r="F22">
         <v>0.02</v>
       </c>
       <c r="G22">
-        <v>19.668</v>
+        <v>19.243</v>
       </c>
       <c r="H22">
-        <v>22.203</v>
+        <v>21.711</v>
       </c>
       <c r="I22">
-        <v>19.656</v>
+        <v>19.175</v>
       </c>
       <c r="J22">
-        <v>22.193</v>
+        <v>21.622</v>
       </c>
       <c r="K22">
-        <v>19.686</v>
+        <v>19.307</v>
       </c>
       <c r="L22">
-        <v>22.223</v>
+        <v>21.754</v>
       </c>
     </row>
     <row r="23">
@@ -1266,34 +1266,34 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>18.992</v>
+        <v>18.385</v>
       </c>
       <c r="D23">
-        <v>0.332</v>
+        <v>0.373</v>
       </c>
       <c r="E23">
-        <v>0.577</v>
+        <v>0.611</v>
       </c>
       <c r="F23">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="G23">
-        <v>17.838</v>
+        <v>17.197</v>
       </c>
       <c r="H23">
-        <v>20.099</v>
+        <v>19.592</v>
       </c>
       <c r="I23">
-        <v>17.812</v>
+        <v>17.214</v>
       </c>
       <c r="J23">
-        <v>20.112</v>
+        <v>19.574</v>
       </c>
       <c r="K23">
-        <v>17.849</v>
+        <v>17.204</v>
       </c>
       <c r="L23">
-        <v>20.149</v>
+        <v>19.565</v>
       </c>
     </row>
     <row r="24">
@@ -1306,34 +1306,34 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>18.769</v>
+        <v>18.262</v>
       </c>
       <c r="D24">
-        <v>0.398</v>
+        <v>0.384</v>
       </c>
       <c r="E24">
-        <v>0.631</v>
+        <v>0.619</v>
       </c>
       <c r="F24">
         <v>0.02</v>
       </c>
       <c r="G24">
-        <v>17.54</v>
+        <v>17.06</v>
       </c>
       <c r="H24">
-        <v>20.011</v>
+        <v>19.488</v>
       </c>
       <c r="I24">
-        <v>17.572</v>
+        <v>17.027</v>
       </c>
       <c r="J24">
-        <v>20</v>
+        <v>19.524</v>
       </c>
       <c r="K24">
-        <v>17.545</v>
+        <v>17.012</v>
       </c>
       <c r="L24">
-        <v>19.973</v>
+        <v>19.51</v>
       </c>
     </row>
     <row r="25">
@@ -1346,34 +1346,34 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>17.058</v>
+        <v>16.918</v>
       </c>
       <c r="D25">
-        <v>0.292</v>
+        <v>0.315</v>
       </c>
       <c r="E25">
-        <v>0.541</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="F25">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="G25">
-        <v>15.988</v>
+        <v>15.798</v>
       </c>
       <c r="H25">
-        <v>18.107</v>
+        <v>17.996</v>
       </c>
       <c r="I25">
-        <v>15.959</v>
+        <v>15.775</v>
       </c>
       <c r="J25">
-        <v>18.102</v>
+        <v>17.973</v>
       </c>
       <c r="K25">
-        <v>16.003</v>
+        <v>15.841</v>
       </c>
       <c r="L25">
-        <v>18.146</v>
+        <v>18.04</v>
       </c>
     </row>
     <row r="26">
@@ -1386,34 +1386,34 @@
         <v>1</v>
       </c>
       <c r="C26">
-        <v>295.616</v>
+        <v>281.966</v>
       </c>
       <c r="D26">
-        <v>6.471</v>
+        <v>6.077</v>
       </c>
       <c r="E26">
-        <v>2.544</v>
+        <v>2.465</v>
       </c>
       <c r="F26">
-        <v>0.08</v>
+        <v>0.078</v>
       </c>
       <c r="G26">
-        <v>290.896</v>
+        <v>277.345</v>
       </c>
       <c r="H26">
-        <v>300.868</v>
+        <v>287.009</v>
       </c>
       <c r="I26">
-        <v>290.826</v>
+        <v>277</v>
       </c>
       <c r="J26">
-        <v>300.924</v>
+        <v>287.166</v>
       </c>
       <c r="K26">
-        <v>290.574</v>
+        <v>276.977</v>
       </c>
       <c r="L26">
-        <v>300.672</v>
+        <v>287.142</v>
       </c>
     </row>
     <row r="27">
@@ -1426,34 +1426,34 @@
         <v>2</v>
       </c>
       <c r="C27">
-        <v>191.34</v>
+        <v>200.671</v>
       </c>
       <c r="D27">
-        <v>3.751</v>
+        <v>4.71</v>
       </c>
       <c r="E27">
-        <v>1.937</v>
+        <v>2.17</v>
       </c>
       <c r="F27">
-        <v>0.061</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G27">
-        <v>187.277</v>
+        <v>196.219</v>
       </c>
       <c r="H27">
-        <v>194.869</v>
+        <v>204.726</v>
       </c>
       <c r="I27">
-        <v>187.315</v>
+        <v>196.148</v>
       </c>
       <c r="J27">
-        <v>194.882</v>
+        <v>204.43</v>
       </c>
       <c r="K27">
-        <v>187.531</v>
+        <v>196.714</v>
       </c>
       <c r="L27">
-        <v>195.098</v>
+        <v>204.996</v>
       </c>
     </row>
     <row r="28">
@@ -1466,34 +1466,34 @@
         <v>3</v>
       </c>
       <c r="C28">
-        <v>127.49</v>
+        <v>137.177</v>
       </c>
       <c r="D28">
-        <v>2.798</v>
+        <v>3.076</v>
       </c>
       <c r="E28">
-        <v>1.673</v>
+        <v>1.754</v>
       </c>
       <c r="F28">
-        <v>0.053</v>
+        <v>0.055</v>
       </c>
       <c r="G28">
-        <v>124.098</v>
+        <v>133.593</v>
       </c>
       <c r="H28">
-        <v>130.655</v>
+        <v>140.468</v>
       </c>
       <c r="I28">
-        <v>124.07</v>
+        <v>133.744</v>
       </c>
       <c r="J28">
-        <v>130.675</v>
+        <v>140.511</v>
       </c>
       <c r="K28">
-        <v>124.191</v>
+        <v>133.697</v>
       </c>
       <c r="L28">
-        <v>130.796</v>
+        <v>140.463</v>
       </c>
     </row>
     <row r="29">
@@ -1506,34 +1506,34 @@
         <v>4</v>
       </c>
       <c r="C29">
-        <v>90.39400000000001</v>
+        <v>95.988</v>
       </c>
       <c r="D29">
-        <v>2.76</v>
+        <v>2.301</v>
       </c>
       <c r="E29">
-        <v>1.661</v>
+        <v>1.517</v>
       </c>
       <c r="F29">
-        <v>0.053</v>
+        <v>0.048</v>
       </c>
       <c r="G29">
-        <v>87.074</v>
+        <v>92.986</v>
       </c>
       <c r="H29">
-        <v>93.587</v>
+        <v>98.932</v>
       </c>
       <c r="I29">
-        <v>86.904</v>
+        <v>92.81399999999999</v>
       </c>
       <c r="J29">
-        <v>93.39</v>
+        <v>98.82899999999999</v>
       </c>
       <c r="K29">
-        <v>87.334</v>
+        <v>93.11799999999999</v>
       </c>
       <c r="L29">
-        <v>93.81999999999999</v>
+        <v>99.133</v>
       </c>
     </row>
     <row r="30">
@@ -1546,34 +1546,34 @@
         <v>5</v>
       </c>
       <c r="C30">
-        <v>70.218</v>
+        <v>73.449</v>
       </c>
       <c r="D30">
-        <v>1.369</v>
+        <v>1.589</v>
       </c>
       <c r="E30">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="F30">
-        <v>0.037</v>
+        <v>0.04</v>
       </c>
       <c r="G30">
-        <v>67.88200000000001</v>
+        <v>71.021</v>
       </c>
       <c r="H30">
-        <v>72.46899999999999</v>
+        <v>75.961</v>
       </c>
       <c r="I30">
-        <v>67.80200000000001</v>
+        <v>70.92400000000001</v>
       </c>
       <c r="J30">
-        <v>72.387</v>
+        <v>75.839</v>
       </c>
       <c r="K30">
-        <v>68.006</v>
+        <v>71.101</v>
       </c>
       <c r="L30">
-        <v>72.59099999999999</v>
+        <v>76.015</v>
       </c>
     </row>
     <row r="31">
@@ -1586,34 +1586,34 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>56.836</v>
+        <v>58.314</v>
       </c>
       <c r="D31">
-        <v>1.081</v>
+        <v>1.164</v>
       </c>
       <c r="E31">
-        <v>1.04</v>
+        <v>1.079</v>
       </c>
       <c r="F31">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
       <c r="G31">
-        <v>54.876</v>
+        <v>56.291</v>
       </c>
       <c r="H31">
-        <v>58.952</v>
+        <v>60.521</v>
       </c>
       <c r="I31">
-        <v>54.874</v>
+        <v>56.239</v>
       </c>
       <c r="J31">
-        <v>59.028</v>
+        <v>60.581</v>
       </c>
       <c r="K31">
-        <v>54.721</v>
+        <v>56.139</v>
       </c>
       <c r="L31">
-        <v>58.875</v>
+        <v>60.48</v>
       </c>
     </row>
     <row r="32">
@@ -1626,34 +1626,34 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <v>49.298</v>
+        <v>49.036</v>
       </c>
       <c r="D32">
-        <v>1.004</v>
+        <v>0.978</v>
       </c>
       <c r="E32">
-        <v>1.002</v>
+        <v>0.989</v>
       </c>
       <c r="F32">
-        <v>0.032</v>
+        <v>0.031</v>
       </c>
       <c r="G32">
-        <v>47.407</v>
+        <v>47.151</v>
       </c>
       <c r="H32">
-        <v>51.334</v>
+        <v>51.027</v>
       </c>
       <c r="I32">
-        <v>47.414</v>
+        <v>47.108</v>
       </c>
       <c r="J32">
-        <v>51.277</v>
+        <v>50.974</v>
       </c>
       <c r="K32">
-        <v>47.391</v>
+        <v>47.151</v>
       </c>
       <c r="L32">
-        <v>51.255</v>
+        <v>51.017</v>
       </c>
     </row>
     <row r="33">
@@ -1666,34 +1666,34 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <v>42.955</v>
+        <v>41.678</v>
       </c>
       <c r="D33">
-        <v>0.928</v>
+        <v>0.872</v>
       </c>
       <c r="E33">
-        <v>0.964</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="F33">
         <v>0.03</v>
       </c>
       <c r="G33">
-        <v>41.092</v>
+        <v>39.859</v>
       </c>
       <c r="H33">
-        <v>44.869</v>
+        <v>43.519</v>
       </c>
       <c r="I33">
-        <v>41.033</v>
+        <v>39.764</v>
       </c>
       <c r="J33">
-        <v>44.763</v>
+        <v>43.393</v>
       </c>
       <c r="K33">
-        <v>41.171</v>
+        <v>39.974</v>
       </c>
       <c r="L33">
-        <v>44.902</v>
+        <v>43.603</v>
       </c>
     </row>
     <row r="34">
@@ -1706,34 +1706,34 @@
         <v>9</v>
       </c>
       <c r="C34">
-        <v>38.388</v>
+        <v>37.478</v>
       </c>
       <c r="D34">
-        <v>0.779</v>
+        <v>0.71</v>
       </c>
       <c r="E34">
-        <v>0.882</v>
+        <v>0.842</v>
       </c>
       <c r="F34">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="G34">
-        <v>36.625</v>
+        <v>35.799</v>
       </c>
       <c r="H34">
-        <v>40.084</v>
+        <v>39.102</v>
       </c>
       <c r="I34">
-        <v>36.743</v>
+        <v>35.767</v>
       </c>
       <c r="J34">
-        <v>40.151</v>
+        <v>39.177</v>
       </c>
       <c r="K34">
-        <v>36.591</v>
+        <v>35.751</v>
       </c>
       <c r="L34">
-        <v>39.999</v>
+        <v>39.162</v>
       </c>
     </row>
     <row r="35">
@@ -1746,34 +1746,34 @@
         <v>10</v>
       </c>
       <c r="C35">
-        <v>36.886</v>
+        <v>35.479</v>
       </c>
       <c r="D35">
-        <v>0.751</v>
+        <v>0.696</v>
       </c>
       <c r="E35">
-        <v>0.866</v>
+        <v>0.834</v>
       </c>
       <c r="F35">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
       <c r="G35">
-        <v>35.23</v>
+        <v>33.858</v>
       </c>
       <c r="H35">
-        <v>38.627</v>
+        <v>37.128</v>
       </c>
       <c r="I35">
-        <v>35.202</v>
+        <v>33.794</v>
       </c>
       <c r="J35">
-        <v>38.59</v>
+        <v>37.109</v>
       </c>
       <c r="K35">
-        <v>35.225</v>
+        <v>33.862</v>
       </c>
       <c r="L35">
-        <v>38.613</v>
+        <v>37.178</v>
       </c>
     </row>
     <row r="36">
@@ -1786,34 +1786,34 @@
         <v>11</v>
       </c>
       <c r="C36">
-        <v>34.472</v>
+        <v>33.371</v>
       </c>
       <c r="D36">
-        <v>0.77</v>
+        <v>0.838</v>
       </c>
       <c r="E36">
-        <v>0.877</v>
+        <v>0.915</v>
       </c>
       <c r="F36">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
       <c r="G36">
-        <v>32.823</v>
+        <v>31.692</v>
       </c>
       <c r="H36">
-        <v>36.262</v>
+        <v>35.28</v>
       </c>
       <c r="I36">
-        <v>32.653</v>
+        <v>31.436</v>
       </c>
       <c r="J36">
-        <v>36.228</v>
+        <v>35.242</v>
       </c>
       <c r="K36">
-        <v>32.787</v>
+        <v>31.615</v>
       </c>
       <c r="L36">
-        <v>36.362</v>
+        <v>35.421</v>
       </c>
     </row>
     <row r="37">
@@ -1826,34 +1826,34 @@
         <v>12</v>
       </c>
       <c r="C37">
-        <v>35.508</v>
+        <v>34.096</v>
       </c>
       <c r="D37">
-        <v>0.754</v>
+        <v>0.701</v>
       </c>
       <c r="E37">
-        <v>0.868</v>
+        <v>0.837</v>
       </c>
       <c r="F37">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
       <c r="G37">
-        <v>33.792</v>
+        <v>32.482</v>
       </c>
       <c r="H37">
-        <v>37.195</v>
+        <v>35.763</v>
       </c>
       <c r="I37">
-        <v>33.736</v>
+        <v>32.572</v>
       </c>
       <c r="J37">
-        <v>37.139</v>
+        <v>35.754</v>
       </c>
       <c r="K37">
-        <v>33.863</v>
+        <v>32.465</v>
       </c>
       <c r="L37">
-        <v>37.266</v>
+        <v>35.646</v>
       </c>
     </row>
     <row r="38">
@@ -1866,34 +1866,34 @@
         <v>13</v>
       </c>
       <c r="C38">
-        <v>30.006</v>
+        <v>28.859</v>
       </c>
       <c r="D38">
-        <v>0.5659999999999999</v>
+        <v>0.514</v>
       </c>
       <c r="E38">
-        <v>0.752</v>
+        <v>0.717</v>
       </c>
       <c r="F38">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="G38">
-        <v>28.625</v>
+        <v>27.547</v>
       </c>
       <c r="H38">
-        <v>31.573</v>
+        <v>30.358</v>
       </c>
       <c r="I38">
-        <v>28.568</v>
+        <v>27.501</v>
       </c>
       <c r="J38">
-        <v>31.617</v>
+        <v>30.304</v>
       </c>
       <c r="K38">
-        <v>28.488</v>
+        <v>27.508</v>
       </c>
       <c r="L38">
-        <v>31.537</v>
+        <v>30.311</v>
       </c>
     </row>
     <row r="39">
@@ -1906,34 +1906,34 @@
         <v>14</v>
       </c>
       <c r="C39">
-        <v>30.641</v>
+        <v>29.002</v>
       </c>
       <c r="D39">
-        <v>0.627</v>
+        <v>0.543</v>
       </c>
       <c r="E39">
-        <v>0.792</v>
+        <v>0.737</v>
       </c>
       <c r="F39">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
       <c r="G39">
-        <v>29.189</v>
+        <v>27.659</v>
       </c>
       <c r="H39">
-        <v>32.292</v>
+        <v>30.546</v>
       </c>
       <c r="I39">
-        <v>29.085</v>
+        <v>27.543</v>
       </c>
       <c r="J39">
-        <v>32.252</v>
+        <v>30.514</v>
       </c>
       <c r="K39">
-        <v>29.129</v>
+        <v>27.591</v>
       </c>
       <c r="L39">
-        <v>32.296</v>
+        <v>30.562</v>
       </c>
     </row>
     <row r="40">
@@ -1946,34 +1946,34 @@
         <v>15</v>
       </c>
       <c r="C40">
-        <v>28.701</v>
+        <v>27.551</v>
       </c>
       <c r="D40">
-        <v>0.595</v>
+        <v>0.53</v>
       </c>
       <c r="E40">
-        <v>0.772</v>
+        <v>0.728</v>
       </c>
       <c r="F40">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="G40">
-        <v>27.198</v>
+        <v>26.129</v>
       </c>
       <c r="H40">
-        <v>30.223</v>
+        <v>28.983</v>
       </c>
       <c r="I40">
-        <v>27.122</v>
+        <v>26.134</v>
       </c>
       <c r="J40">
-        <v>30.203</v>
+        <v>28.947</v>
       </c>
       <c r="K40">
-        <v>27.208</v>
+        <v>26.161</v>
       </c>
       <c r="L40">
-        <v>30.289</v>
+        <v>28.973</v>
       </c>
     </row>
     <row r="41">
@@ -1986,34 +1986,34 @@
         <v>16</v>
       </c>
       <c r="C41">
-        <v>28.285</v>
+        <v>27.144</v>
       </c>
       <c r="D41">
-        <v>0.595</v>
+        <v>0.599</v>
       </c>
       <c r="E41">
-        <v>0.771</v>
+        <v>0.774</v>
       </c>
       <c r="F41">
         <v>0.024</v>
       </c>
       <c r="G41">
-        <v>26.72</v>
+        <v>25.569</v>
       </c>
       <c r="H41">
-        <v>29.743</v>
+        <v>28.603</v>
       </c>
       <c r="I41">
-        <v>26.699</v>
+        <v>25.533</v>
       </c>
       <c r="J41">
-        <v>29.676</v>
+        <v>28.533</v>
       </c>
       <c r="K41">
-        <v>26.841</v>
+        <v>25.698</v>
       </c>
       <c r="L41">
-        <v>29.818</v>
+        <v>28.697</v>
       </c>
     </row>
     <row r="42">
@@ -2026,34 +2026,34 @@
         <v>17</v>
       </c>
       <c r="C42">
-        <v>28.13</v>
+        <v>26.597</v>
       </c>
       <c r="D42">
-        <v>0.585</v>
+        <v>0.525</v>
       </c>
       <c r="E42">
-        <v>0.765</v>
+        <v>0.725</v>
       </c>
       <c r="F42">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="G42">
-        <v>26.673</v>
+        <v>25.161</v>
       </c>
       <c r="H42">
-        <v>29.671</v>
+        <v>28.002</v>
       </c>
       <c r="I42">
-        <v>26.715</v>
+        <v>25.062</v>
       </c>
       <c r="J42">
-        <v>29.612</v>
+        <v>27.954</v>
       </c>
       <c r="K42">
-        <v>26.69</v>
+        <v>25.224</v>
       </c>
       <c r="L42">
-        <v>29.587</v>
+        <v>28.117</v>
       </c>
     </row>
     <row r="43">
@@ -2066,34 +2066,34 @@
         <v>18</v>
       </c>
       <c r="C43">
-        <v>25.578</v>
+        <v>24.527</v>
       </c>
       <c r="D43">
-        <v>0.527</v>
+        <v>0.49</v>
       </c>
       <c r="E43">
-        <v>0.726</v>
+        <v>0.7</v>
       </c>
       <c r="F43">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="G43">
-        <v>24.14</v>
+        <v>23.132</v>
       </c>
       <c r="H43">
-        <v>26.984</v>
+        <v>25.876</v>
       </c>
       <c r="I43">
-        <v>24.091</v>
+        <v>23.079</v>
       </c>
       <c r="J43">
-        <v>26.935</v>
+        <v>25.86</v>
       </c>
       <c r="K43">
-        <v>24.205</v>
+        <v>23.17</v>
       </c>
       <c r="L43">
-        <v>27.049</v>
+        <v>25.951</v>
       </c>
     </row>
     <row r="44">
@@ -2106,34 +2106,34 @@
         <v>19</v>
       </c>
       <c r="C44">
-        <v>25.204</v>
+        <v>23.996</v>
       </c>
       <c r="D44">
-        <v>0.964</v>
+        <v>0.489</v>
       </c>
       <c r="E44">
-        <v>0.982</v>
+        <v>0.699</v>
       </c>
       <c r="F44">
-        <v>0.031</v>
+        <v>0.022</v>
       </c>
       <c r="G44">
-        <v>23.345</v>
+        <v>22.678</v>
       </c>
       <c r="H44">
-        <v>27.194</v>
+        <v>25.419</v>
       </c>
       <c r="I44">
-        <v>23.176</v>
+        <v>22.706</v>
       </c>
       <c r="J44">
-        <v>27.031</v>
+        <v>25.415</v>
       </c>
       <c r="K44">
-        <v>23.443</v>
+        <v>22.63</v>
       </c>
       <c r="L44">
-        <v>27.297</v>
+        <v>25.339</v>
       </c>
     </row>
     <row r="45">
@@ -2146,34 +2146,34 @@
         <v>20</v>
       </c>
       <c r="C45">
-        <v>24.095</v>
+        <v>23.382</v>
       </c>
       <c r="D45">
-        <v>0.506</v>
+        <v>0.494</v>
       </c>
       <c r="E45">
-        <v>0.711</v>
+        <v>0.703</v>
       </c>
       <c r="F45">
         <v>0.022</v>
       </c>
       <c r="G45">
-        <v>22.676</v>
+        <v>21.974</v>
       </c>
       <c r="H45">
-        <v>25.464</v>
+        <v>24.73</v>
       </c>
       <c r="I45">
-        <v>22.67</v>
+        <v>21.932</v>
       </c>
       <c r="J45">
-        <v>25.418</v>
+        <v>24.715</v>
       </c>
       <c r="K45">
-        <v>22.747</v>
+        <v>22.019</v>
       </c>
       <c r="L45">
-        <v>25.495</v>
+        <v>24.802</v>
       </c>
     </row>
     <row r="46">
@@ -2186,34 +2186,34 @@
         <v>21</v>
       </c>
       <c r="C46">
-        <v>23.398</v>
+        <v>22.879</v>
       </c>
       <c r="D46">
-        <v>0.513</v>
+        <v>0.525</v>
       </c>
       <c r="E46">
-        <v>0.716</v>
+        <v>0.725</v>
       </c>
       <c r="F46">
         <v>0.023</v>
       </c>
       <c r="G46">
-        <v>21.965</v>
+        <v>21.406</v>
       </c>
       <c r="H46">
-        <v>24.773</v>
+        <v>24.247</v>
       </c>
       <c r="I46">
-        <v>21.929</v>
+        <v>21.359</v>
       </c>
       <c r="J46">
-        <v>24.718</v>
+        <v>24.215</v>
       </c>
       <c r="K46">
-        <v>22.05</v>
+        <v>21.491</v>
       </c>
       <c r="L46">
-        <v>24.839</v>
+        <v>24.346</v>
       </c>
     </row>
     <row r="47">
@@ -2226,34 +2226,34 @@
         <v>22</v>
       </c>
       <c r="C47">
-        <v>21.165</v>
+        <v>20.507</v>
       </c>
       <c r="D47">
-        <v>0.43</v>
+        <v>0.472</v>
       </c>
       <c r="E47">
-        <v>0.655</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="F47">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="G47">
-        <v>19.941</v>
+        <v>19.219</v>
       </c>
       <c r="H47">
-        <v>22.511</v>
+        <v>21.911</v>
       </c>
       <c r="I47">
-        <v>20.01</v>
+        <v>19.257</v>
       </c>
       <c r="J47">
-        <v>22.48</v>
+        <v>21.906</v>
       </c>
       <c r="K47">
-        <v>19.911</v>
+        <v>19.165</v>
       </c>
       <c r="L47">
-        <v>22.381</v>
+        <v>21.814</v>
       </c>
     </row>
     <row r="48">
@@ -2266,34 +2266,34 @@
         <v>23</v>
       </c>
       <c r="C48">
-        <v>20.988</v>
+        <v>20.425</v>
       </c>
       <c r="D48">
-        <v>0.492</v>
+        <v>0.473</v>
       </c>
       <c r="E48">
-        <v>0.702</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="F48">
         <v>0.022</v>
       </c>
       <c r="G48">
-        <v>19.564</v>
+        <v>19.027</v>
       </c>
       <c r="H48">
-        <v>22.314</v>
+        <v>21.723</v>
       </c>
       <c r="I48">
-        <v>19.55</v>
+        <v>18.981</v>
       </c>
       <c r="J48">
-        <v>22.224</v>
+        <v>21.59</v>
       </c>
       <c r="K48">
-        <v>19.703</v>
+        <v>19.211</v>
       </c>
       <c r="L48">
-        <v>22.377</v>
+        <v>21.819</v>
       </c>
     </row>
     <row r="49">
@@ -2306,34 +2306,34 @@
         <v>24</v>
       </c>
       <c r="C49">
-        <v>19.056</v>
+        <v>18.905</v>
       </c>
       <c r="D49">
-        <v>0.352</v>
+        <v>0.4</v>
       </c>
       <c r="E49">
-        <v>0.593</v>
+        <v>0.632</v>
       </c>
       <c r="F49">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="G49">
-        <v>17.867</v>
+        <v>17.617</v>
       </c>
       <c r="H49">
-        <v>20.192</v>
+        <v>20.096</v>
       </c>
       <c r="I49">
-        <v>17.708</v>
+        <v>17.515</v>
       </c>
       <c r="J49">
-        <v>20.165</v>
+        <v>20.122</v>
       </c>
       <c r="K49">
-        <v>17.92</v>
+        <v>17.64</v>
       </c>
       <c r="L49">
-        <v>20.377</v>
+        <v>20.247</v>
       </c>
     </row>
   </sheetData>
